--- a/FileRaw/Calendario interventi.xlsx
+++ b/FileRaw/Calendario interventi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadepaoli/Documents/Coding/cDen/chipdent/FileRaw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC48CDF4-4578-4501-AA72-319FBC3558E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29ED5715-C84F-A042-9C7B-84E5E83136C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{DCEA0645-F501-4F35-BFFE-40E6EE365336}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29460" windowHeight="18980" xr2:uid="{DCEA0645-F501-4F35-BFFE-40E6EE365336}"/>
   </bookViews>
   <sheets>
     <sheet name="PLANNING APERTURA - TO DO" sheetId="12" r:id="rId1"/>
@@ -56,10 +56,10 @@
   <commentList>
     <comment ref="A6" authorId="0" shapeId="0" xr:uid="{20861A30-B3FE-4EB0-B190-3F4B968F6F1F}">
       <text>
-        <t>[Commento in thread]
-La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
-Commento:
-quando varia vi è da svolgere comunicazione all’ATS :
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    quando varia vi è da svolgere comunicazione all’ATS :
 - NUOVO ALLEGATO F
 - AUTOCERTIFICAZIONE
 - DOC DI IDENTITA’</t>
@@ -67,19 +67,19 @@
     </comment>
     <comment ref="A9" authorId="1" shapeId="0" xr:uid="{25E39706-9B82-4C6F-886C-5449256CD707}">
       <text>
-        <t>[Commento in thread]
-La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
-Commento:
-DA AGGIORNARE ad ogni variazione del personale medico (invio pec ATS) 
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    DA AGGIORNARE ad ogni variazione del personale medico (invio pec ATS) 
 testo mail: “annulla e sostituisce il precedente”</t>
       </text>
     </comment>
     <comment ref="A37" authorId="2" shapeId="0" xr:uid="{A14E2391-7E41-4A35-BDC5-FA80311C788F}">
       <text>
-        <t>[Commento in thread]
-La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
-Commento:
-È lo Studio a gestire i passaggi.
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    È lo Studio a gestire i passaggi.
 1. devono avere il registro, va compilato in fase di ritiro
 2. inizialmente 3 ROT (bidoni) che poi diventano 5
 3. x il passaggio x ritiro: ALMENO 2 rot pieni + spore (ctrl autoclavi)</t>
@@ -87,10 +87,10 @@
     </comment>
     <comment ref="A41" authorId="3" shapeId="0" xr:uid="{747419CA-4163-4DD7-B9A0-FBD871F81339}">
       <text>
-        <t>[Commento in thread]
-La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
-Commento:
-Roberta Giuliano - uff. amm.
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Roberta Giuliano - uff. amm.
 r.giuliano@cristalgroup.it
 Grazia Colombo - uff. comm. 
 commerciale@cristalcooperativa.it
@@ -906,7 +906,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-410]mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-410]mmm\-yy;@"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1935,11 +1935,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1961,11 +1961,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1975,19 +2013,49 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="17" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="12" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="12" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1995,43 +2063,27 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="12" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="12" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2056,68 +2108,22 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="12" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2129,38 +2135,38 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2194,21 +2200,12 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2218,18 +2215,111 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2251,107 +2341,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Valuta" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="31">
     <dxf>
@@ -4402,21 +4402,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9055C-23B1-47C1-9C84-B69AC13ABD75}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.45" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="77.33203125" style="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="33.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.1640625" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" style="17"/>
     <col min="7" max="7" width="13.6640625" style="17" customWidth="1"/>
     <col min="8" max="8" width="44" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" style="17" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>124</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>126</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>127</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>4</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>9</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
@@ -4535,11 +4535,11 @@
       <c r="D9" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="89" t="b">
+      <c r="I9" s="100" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>12</v>
       </c>
@@ -4553,9 +4553,9 @@
       <c r="E10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="89"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="100"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>15</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="104" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>17</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="26" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>18</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>21</v>
       </c>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E14" s="20"/>
     </row>
-    <row r="15" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>22</v>
       </c>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E15" s="20"/>
     </row>
-    <row r="16" spans="1:9" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>23</v>
       </c>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="E16" s="20"/>
     </row>
-    <row r="17" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E17" s="20"/>
     </row>
-    <row r="18" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>26</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
     </row>
-    <row r="19" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>28</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>30</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>32</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>33</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>35</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
         <v>36</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
         <v>37</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
         <v>38</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>39</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>40</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
         <v>41</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>42</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>43</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>44</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>45</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>46</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>47</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>48</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>50</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>53</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>54</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
         <v>130</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>128</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>129</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>55</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
         <v>56</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
         <v>123</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="26" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
         <v>57</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
         <v>59</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
         <v>60</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
         <v>62</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
         <v>63</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
         <v>64</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
         <v>65</v>
       </c>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="H52" s="17"/>
     </row>
-    <row r="53" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
         <v>67</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="15" t="s">
         <v>69</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
         <v>71</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
         <v>131</v>
       </c>
@@ -5099,23 +5099,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G58" s="1"/>
       <c r="H58" s="17"/>
     </row>
-    <row r="59" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G59" s="1"/>
       <c r="H59" s="17"/>
     </row>
-    <row r="60" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G60" s="1"/>
       <c r="H60" s="17"/>
     </row>
-    <row r="61" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G61" s="1"/>
       <c r="H61" s="17"/>
     </row>
-    <row r="62" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G62" s="1"/>
       <c r="H62" s="17"/>
     </row>
@@ -5128,6 +5128,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>
 </worksheet>
@@ -5137,506 +5140,494 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B15A8A-C0C1-4836-9AFD-C2C91AC6D38C}">
   <sheetPr codeName="Foglio7"/>
   <dimension ref="B4:W28"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.2">
       <c r="R4" s="73">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="14" spans="2:23" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" s="7" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B14" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="C14" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="100" t="s">
+      <c r="D14" s="95"/>
+      <c r="E14" s="105" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="100"/>
-      <c r="G14" s="99" t="s">
+      <c r="F14" s="105"/>
+      <c r="G14" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="98" t="s">
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="98"/>
-      <c r="O14" s="98"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="98"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
+      <c r="R14" s="95"/>
+      <c r="S14" s="95"/>
       <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="92">
+      <c r="C15" s="101">
         <v>46054</v>
       </c>
-      <c r="D15" s="93"/>
-      <c r="E15" s="94" t="b">
+      <c r="D15" s="102"/>
+      <c r="E15" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="95">
+      <c r="F15" s="89"/>
+      <c r="G15" s="90">
         <v>46235</v>
       </c>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="90" t="s">
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="93" t="s">
         <v>217</v>
       </c>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="94"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
+      <c r="S15" s="94"/>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="92">
+      <c r="C16" s="101">
         <v>46023</v>
       </c>
-      <c r="D16" s="93"/>
-      <c r="E16" s="94" t="b">
+      <c r="D16" s="102"/>
+      <c r="E16" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="94"/>
-      <c r="G16" s="95">
+      <c r="F16" s="89"/>
+      <c r="G16" s="90">
         <v>46204</v>
       </c>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="90" t="s">
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="93" t="s">
         <v>221</v>
       </c>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="91"/>
-      <c r="S16" s="91"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+      <c r="S16" s="94"/>
       <c r="W16" s="1"/>
     </row>
-    <row r="17" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="101">
         <v>46023</v>
       </c>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94" t="b">
+      <c r="D17" s="102"/>
+      <c r="E17" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="95">
+      <c r="F17" s="89"/>
+      <c r="G17" s="90">
         <v>46204</v>
       </c>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="90" t="s">
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="94"/>
+      <c r="Q17" s="94"/>
+      <c r="R17" s="94"/>
+      <c r="S17" s="94"/>
       <c r="W17" s="1"/>
     </row>
-    <row r="18" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="92">
+      <c r="C18" s="101">
         <v>46023</v>
       </c>
-      <c r="D18" s="93"/>
-      <c r="E18" s="94" t="b">
+      <c r="D18" s="102"/>
+      <c r="E18" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="94"/>
-      <c r="G18" s="95">
+      <c r="F18" s="89"/>
+      <c r="G18" s="90">
         <v>46204</v>
       </c>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="90" t="s">
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="93" t="s">
         <v>222</v>
       </c>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="91"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="92">
+      <c r="C19" s="101">
         <v>46023</v>
       </c>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94" t="b">
+      <c r="D19" s="102"/>
+      <c r="E19" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="95">
+      <c r="F19" s="89"/>
+      <c r="G19" s="90">
         <v>46204</v>
       </c>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="90" t="s">
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="93" t="s">
         <v>223</v>
       </c>
-      <c r="L19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="91"/>
-      <c r="R19" s="91"/>
-      <c r="S19" s="91"/>
-    </row>
-    <row r="20" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="94"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+    </row>
+    <row r="20" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="101">
+      <c r="C20" s="103">
         <v>45717</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="94" t="b">
+      <c r="D20" s="104"/>
+      <c r="E20" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="95">
+      <c r="F20" s="89"/>
+      <c r="G20" s="90">
         <v>46266</v>
       </c>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="90" t="s">
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="93" t="s">
         <v>218</v>
       </c>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="91"/>
-      <c r="R20" s="91"/>
-      <c r="S20" s="91"/>
-    </row>
-    <row r="21" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="94"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+    </row>
+    <row r="21" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="101">
+      <c r="C21" s="103">
         <v>45717</v>
       </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="94" t="b">
+      <c r="D21" s="104"/>
+      <c r="E21" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="94"/>
-      <c r="G21" s="95">
+      <c r="F21" s="89"/>
+      <c r="G21" s="90">
         <v>46266</v>
       </c>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="90" t="s">
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="93" t="s">
         <v>218</v>
       </c>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="91"/>
-      <c r="Q21" s="91"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="91"/>
-    </row>
-    <row r="22" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="94"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="94"/>
+    </row>
+    <row r="22" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="92">
+      <c r="C22" s="101">
         <v>46023</v>
       </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="94" t="b">
+      <c r="D22" s="102"/>
+      <c r="E22" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F22" s="94"/>
-      <c r="G22" s="95">
+      <c r="F22" s="89"/>
+      <c r="G22" s="90">
         <v>46204</v>
       </c>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="90" t="s">
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="93" t="s">
         <v>224</v>
       </c>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="91"/>
-      <c r="R22" s="91"/>
-      <c r="S22" s="91"/>
-    </row>
-    <row r="23" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+    </row>
+    <row r="23" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="101">
+      <c r="C23" s="103">
         <v>46082</v>
       </c>
-      <c r="D23" s="102"/>
-      <c r="E23" s="94" t="b">
+      <c r="D23" s="104"/>
+      <c r="E23" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="95">
+      <c r="F23" s="89"/>
+      <c r="G23" s="90">
         <v>46266</v>
       </c>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="90" t="s">
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-    </row>
-    <row r="24" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="94"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="94"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+      <c r="S23" s="94"/>
+    </row>
+    <row r="24" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="92">
+      <c r="C24" s="101">
         <v>46082</v>
       </c>
-      <c r="D24" s="93"/>
-      <c r="E24" s="94" t="b">
+      <c r="D24" s="102"/>
+      <c r="E24" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F24" s="94"/>
-      <c r="G24" s="95">
+      <c r="F24" s="89"/>
+      <c r="G24" s="90">
         <v>46266</v>
       </c>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="90" t="s">
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
-      <c r="R24" s="91"/>
-      <c r="S24" s="91"/>
-    </row>
-    <row r="25" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L24" s="94"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="94"/>
+      <c r="R24" s="94"/>
+      <c r="S24" s="94"/>
+    </row>
+    <row r="25" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="101">
         <v>46023</v>
       </c>
-      <c r="D25" s="93"/>
-      <c r="E25" s="94" t="b">
+      <c r="D25" s="102"/>
+      <c r="E25" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="94"/>
-      <c r="G25" s="95">
+      <c r="F25" s="89"/>
+      <c r="G25" s="90">
         <v>46204</v>
       </c>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="90" t="s">
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="93" t="s">
         <v>225</v>
       </c>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="91"/>
-      <c r="S25" s="91"/>
-    </row>
-    <row r="26" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L25" s="94"/>
+      <c r="M25" s="94"/>
+      <c r="N25" s="94"/>
+      <c r="O25" s="94"/>
+      <c r="P25" s="94"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="94"/>
+      <c r="S25" s="94"/>
+    </row>
+    <row r="26" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B26" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="92">
+      <c r="C26" s="101">
         <v>46082</v>
       </c>
-      <c r="D26" s="93"/>
-      <c r="E26" s="94" t="b">
+      <c r="D26" s="102"/>
+      <c r="E26" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F26" s="94"/>
-      <c r="G26" s="95">
+      <c r="F26" s="89"/>
+      <c r="G26" s="90">
         <v>46266</v>
       </c>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="90" t="s">
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="93" t="s">
         <v>218</v>
       </c>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="91"/>
-      <c r="Q26" s="91"/>
-      <c r="R26" s="91"/>
-      <c r="S26" s="91"/>
-    </row>
-    <row r="27" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L26" s="94"/>
+      <c r="M26" s="94"/>
+      <c r="N26" s="94"/>
+      <c r="O26" s="94"/>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="94"/>
+      <c r="R26" s="94"/>
+      <c r="S26" s="94"/>
+    </row>
+    <row r="27" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="92">
+      <c r="C27" s="101">
         <v>45992</v>
       </c>
-      <c r="D27" s="93"/>
-      <c r="E27" s="94" t="b">
+      <c r="D27" s="102"/>
+      <c r="E27" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F27" s="94"/>
-      <c r="G27" s="95">
+      <c r="F27" s="89"/>
+      <c r="G27" s="90">
         <v>46174</v>
       </c>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="90" t="s">
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="93" t="s">
         <v>220</v>
       </c>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="91"/>
-    </row>
-    <row r="28" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L27" s="94"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+    </row>
+    <row r="28" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B28" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C28" s="92">
+      <c r="C28" s="101">
         <v>46113</v>
       </c>
-      <c r="D28" s="93"/>
-      <c r="E28" s="94" t="b">
+      <c r="D28" s="102"/>
+      <c r="E28" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F28" s="94"/>
-      <c r="G28" s="95">
+      <c r="F28" s="89"/>
+      <c r="G28" s="90">
         <v>46296</v>
       </c>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="90" t="s">
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="93" t="s">
         <v>232</v>
       </c>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="91"/>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="91"/>
-      <c r="S28" s="91"/>
+      <c r="L28" s="94"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="94"/>
+      <c r="O28" s="94"/>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="94"/>
+      <c r="R28" s="94"/>
+      <c r="S28" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:S27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:S25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:S26"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="K28:S28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K19:S19"/>
+    <mergeCell ref="K20:S20"/>
+    <mergeCell ref="K21:S21"/>
+    <mergeCell ref="K22:S22"/>
+    <mergeCell ref="K23:S23"/>
+    <mergeCell ref="K24:S24"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G19:J19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="K14:S14"/>
     <mergeCell ref="K15:S15"/>
@@ -5653,22 +5644,34 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
-    <mergeCell ref="K28:S28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K19:S19"/>
-    <mergeCell ref="K20:S20"/>
-    <mergeCell ref="K21:S21"/>
-    <mergeCell ref="K22:S22"/>
-    <mergeCell ref="K23:S23"/>
-    <mergeCell ref="K24:S24"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:S27"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:S25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:S26"/>
   </mergeCells>
   <conditionalFormatting sqref="G15:G28">
     <cfRule type="cellIs" dxfId="30" priority="21" operator="greaterThanOrEqual">
@@ -5690,6 +5693,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5698,516 +5704,488 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C64CC92-BBF9-438F-91D5-251258E06253}">
   <sheetPr codeName="Foglio8"/>
   <dimension ref="B3:W26"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="3" max="4" width="8.6640625" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="Q3" s="73">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" s="7" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B12" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="107" t="s">
+      <c r="D12" s="95"/>
+      <c r="E12" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="107"/>
-      <c r="G12" s="99" t="s">
+      <c r="F12" s="96"/>
+      <c r="G12" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="98" t="s">
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="95"/>
+      <c r="O12" s="95"/>
+      <c r="P12" s="95"/>
+      <c r="Q12" s="95"/>
+      <c r="R12" s="95"/>
+      <c r="S12" s="95"/>
       <c r="W12" s="1"/>
     </row>
-    <row r="13" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="103">
+      <c r="C13" s="87">
         <v>46023</v>
       </c>
-      <c r="D13" s="104"/>
-      <c r="E13" s="94" t="b">
+      <c r="D13" s="88"/>
+      <c r="E13" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F13" s="94"/>
-      <c r="G13" s="95">
+      <c r="F13" s="89"/>
+      <c r="G13" s="90">
         <v>46204</v>
       </c>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="90" t="s">
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="91"/>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="91"/>
-      <c r="S13" s="91"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
       <c r="W13" s="1"/>
     </row>
-    <row r="14" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="103">
+      <c r="C14" s="87">
         <v>46023</v>
       </c>
-      <c r="D14" s="104"/>
-      <c r="E14" s="94" t="b">
+      <c r="D14" s="88"/>
+      <c r="E14" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="94"/>
-      <c r="G14" s="95">
+      <c r="F14" s="89"/>
+      <c r="G14" s="90">
         <v>46204</v>
       </c>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="90" t="s">
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="93" t="s">
         <v>191</v>
       </c>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="91"/>
-      <c r="S14" s="91"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="94"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+      <c r="S14" s="94"/>
       <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="103">
+      <c r="C15" s="87">
         <v>46023</v>
       </c>
-      <c r="D15" s="104"/>
-      <c r="E15" s="94" t="b">
+      <c r="D15" s="88"/>
+      <c r="E15" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="95">
+      <c r="F15" s="89"/>
+      <c r="G15" s="90">
         <v>46204</v>
       </c>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="90" t="s">
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="94"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
+      <c r="S15" s="94"/>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="103">
+      <c r="C16" s="87">
         <v>46023</v>
       </c>
-      <c r="D16" s="104"/>
-      <c r="E16" s="94" t="b">
+      <c r="D16" s="88"/>
+      <c r="E16" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="94"/>
-      <c r="G16" s="95">
+      <c r="F16" s="89"/>
+      <c r="G16" s="90">
         <v>46204</v>
       </c>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="90" t="s">
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="91"/>
-      <c r="S16" s="91"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+      <c r="S16" s="94"/>
       <c r="W16" s="1"/>
     </row>
-    <row r="17" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="103">
+      <c r="C17" s="87">
         <v>46023</v>
       </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="94" t="b">
+      <c r="D17" s="88"/>
+      <c r="E17" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="95">
+      <c r="F17" s="89"/>
+      <c r="G17" s="90">
         <v>46204</v>
       </c>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="90" t="s">
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="93" t="s">
         <v>191</v>
       </c>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-    </row>
-    <row r="18" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="94"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="94"/>
+      <c r="Q17" s="94"/>
+      <c r="R17" s="94"/>
+      <c r="S17" s="94"/>
+    </row>
+    <row r="18" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="103">
+      <c r="C18" s="87">
         <v>46023</v>
       </c>
-      <c r="D18" s="104"/>
-      <c r="E18" s="94" t="b">
+      <c r="D18" s="88"/>
+      <c r="E18" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="94"/>
-      <c r="G18" s="95">
+      <c r="F18" s="89"/>
+      <c r="G18" s="90">
         <v>46204</v>
       </c>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="90" t="s">
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="93" t="s">
         <v>192</v>
       </c>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="91"/>
-    </row>
-    <row r="19" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="94"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+    </row>
+    <row r="19" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="103">
+      <c r="C19" s="87">
         <v>46023</v>
       </c>
-      <c r="D19" s="104"/>
-      <c r="E19" s="94" t="b">
+      <c r="D19" s="88"/>
+      <c r="E19" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="95">
+      <c r="F19" s="89"/>
+      <c r="G19" s="90">
         <v>46204</v>
       </c>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="90" t="s">
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="L19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="91"/>
-      <c r="R19" s="91"/>
-      <c r="S19" s="91"/>
-    </row>
-    <row r="20" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="94"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+    </row>
+    <row r="20" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="103">
+      <c r="C20" s="87">
         <v>46023</v>
       </c>
-      <c r="D20" s="104"/>
-      <c r="E20" s="94" t="b">
+      <c r="D20" s="88"/>
+      <c r="E20" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="95">
+      <c r="F20" s="89"/>
+      <c r="G20" s="90">
         <v>46204</v>
       </c>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="90" t="s">
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="93" t="s">
         <v>192</v>
       </c>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="91"/>
-      <c r="R20" s="91"/>
-      <c r="S20" s="91"/>
-    </row>
-    <row r="21" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="94"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+    </row>
+    <row r="21" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="105">
+      <c r="C21" s="98">
         <v>46113</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="94" t="b">
+      <c r="D21" s="99"/>
+      <c r="E21" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="94"/>
-      <c r="G21" s="95">
+      <c r="F21" s="89"/>
+      <c r="G21" s="90">
         <v>46296</v>
       </c>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="90" t="s">
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="91"/>
-      <c r="Q21" s="91"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="91"/>
-    </row>
-    <row r="22" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="94"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="94"/>
+    </row>
+    <row r="22" spans="2:19" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="103">
+      <c r="C22" s="87">
         <v>46023</v>
       </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="94" t="b">
+      <c r="D22" s="88"/>
+      <c r="E22" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F22" s="94"/>
-      <c r="G22" s="95">
+      <c r="F22" s="89"/>
+      <c r="G22" s="90">
         <v>46235</v>
       </c>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="90" t="s">
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="91"/>
-      <c r="R22" s="91"/>
-      <c r="S22" s="91"/>
-    </row>
-    <row r="23" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+    </row>
+    <row r="23" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="103">
+      <c r="C23" s="87">
         <v>46113</v>
       </c>
-      <c r="D23" s="104"/>
-      <c r="E23" s="94" t="b">
+      <c r="D23" s="88"/>
+      <c r="E23" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="95">
+      <c r="F23" s="89"/>
+      <c r="G23" s="90">
         <v>46296</v>
       </c>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="90" t="s">
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-    </row>
-    <row r="24" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="94"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="94"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+      <c r="S23" s="94"/>
+    </row>
+    <row r="24" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="103">
+      <c r="C24" s="87">
         <v>46023</v>
       </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="94" t="b">
+      <c r="D24" s="88"/>
+      <c r="E24" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F24" s="94"/>
-      <c r="G24" s="95">
+      <c r="F24" s="89"/>
+      <c r="G24" s="90">
         <v>46204</v>
       </c>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="90" t="s">
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
-      <c r="R24" s="91"/>
-      <c r="S24" s="91"/>
-    </row>
-    <row r="25" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="94"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="94"/>
+      <c r="R24" s="94"/>
+      <c r="S24" s="94"/>
+    </row>
+    <row r="25" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="103">
+      <c r="C25" s="87">
         <v>46023</v>
       </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="94" t="b">
+      <c r="D25" s="88"/>
+      <c r="E25" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="94"/>
-      <c r="G25" s="95">
+      <c r="F25" s="89"/>
+      <c r="G25" s="90">
         <v>46204</v>
       </c>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="90" t="s">
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="91"/>
-      <c r="S25" s="91"/>
-    </row>
-    <row r="26" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L25" s="94"/>
+      <c r="M25" s="94"/>
+      <c r="N25" s="94"/>
+      <c r="O25" s="94"/>
+      <c r="P25" s="94"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="94"/>
+      <c r="S25" s="94"/>
+    </row>
+    <row r="26" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B26" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C26" s="103">
+      <c r="C26" s="87">
         <v>46113</v>
       </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="94" t="b">
+      <c r="D26" s="88"/>
+      <c r="E26" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="F26" s="94"/>
-      <c r="G26" s="95">
+      <c r="F26" s="89"/>
+      <c r="G26" s="90">
         <v>46296</v>
       </c>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="90" t="s">
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="91"/>
-      <c r="Q26" s="91"/>
-      <c r="R26" s="91"/>
-      <c r="S26" s="91"/>
+      <c r="L26" s="94"/>
+      <c r="M26" s="94"/>
+      <c r="N26" s="94"/>
+      <c r="O26" s="94"/>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="94"/>
+      <c r="R26" s="94"/>
+      <c r="S26" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="K12:S12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:S13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:S16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:S17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:S18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:S19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:S20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:S23"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:S21"/>
     <mergeCell ref="K26:S26"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
@@ -6224,14 +6202,42 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="K24:S24"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:S23"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:S21"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:S19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:S20"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:S17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:S18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:S16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="K12:S12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:S13"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G26">
     <cfRule type="cellIs" dxfId="25" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
@@ -6254,6 +6260,9 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6261,1492 +6270,1511 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD1E291-C0F0-47E4-9A58-142296219A8E}">
   <dimension ref="B2:W56"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" customWidth="1"/>
-    <col min="19" max="19" width="18.109375" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" customWidth="1"/>
+    <col min="19" max="19" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.2">
       <c r="R2" s="73">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="4" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:23" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="130" t="s">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:23" ht="22" x14ac:dyDescent="0.3">
+      <c r="B5" s="132" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="131"/>
-      <c r="J5" s="131"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="131"/>
-      <c r="M5" s="131"/>
-      <c r="N5" s="131"/>
-      <c r="O5" s="131"/>
-      <c r="P5" s="131"/>
-      <c r="Q5" s="131"/>
-      <c r="R5" s="131"/>
-      <c r="S5" s="132"/>
-    </row>
-    <row r="6" spans="2:23" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="133"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
+    </row>
+    <row r="6" spans="2:23" s="7" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B6" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="133" t="s">
+      <c r="C6" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="134"/>
-      <c r="E6" s="135" t="s">
+      <c r="D6" s="107"/>
+      <c r="E6" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="136"/>
-      <c r="G6" s="137" t="s">
+      <c r="F6" s="109"/>
+      <c r="G6" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="98" t="s">
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="98"/>
-      <c r="Q6" s="98"/>
-      <c r="R6" s="98"/>
-      <c r="S6" s="140"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="95"/>
+      <c r="Q6" s="95"/>
+      <c r="R6" s="95"/>
+      <c r="S6" s="113"/>
       <c r="W6" s="1"/>
     </row>
-    <row r="7" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="101">
+      <c r="C7" s="103">
         <v>45566</v>
       </c>
-      <c r="D7" s="126"/>
-      <c r="E7" s="123" t="b">
+      <c r="D7" s="114"/>
+      <c r="E7" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="124"/>
-      <c r="G7" s="95">
+      <c r="F7" s="116"/>
+      <c r="G7" s="90">
         <v>46296</v>
       </c>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="127" t="s">
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="117" t="s">
         <v>156</v>
       </c>
-      <c r="L7" s="128"/>
-      <c r="M7" s="128"/>
-      <c r="N7" s="128"/>
-      <c r="O7" s="128"/>
-      <c r="P7" s="128"/>
-      <c r="Q7" s="128"/>
-      <c r="R7" s="128"/>
-      <c r="S7" s="129"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118"/>
+      <c r="S7" s="119"/>
       <c r="W7" s="1"/>
     </row>
-    <row r="8" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="101">
+      <c r="C8" s="103">
         <v>45809</v>
       </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="123" t="b">
+      <c r="D8" s="114"/>
+      <c r="E8" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="124"/>
-      <c r="G8" s="95">
+      <c r="F8" s="116"/>
+      <c r="G8" s="90">
         <v>46508</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="97"/>
-      <c r="K8" s="127" t="s">
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="L8" s="128"/>
-      <c r="M8" s="128"/>
-      <c r="N8" s="128"/>
-      <c r="O8" s="128"/>
-      <c r="P8" s="128"/>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
-      <c r="S8" s="129"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="118"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="118"/>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="119"/>
       <c r="W8" s="1"/>
     </row>
-    <row r="9" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="101">
+      <c r="C9" s="103">
         <v>46029</v>
       </c>
-      <c r="D9" s="126"/>
-      <c r="E9" s="123" t="b">
+      <c r="D9" s="114"/>
+      <c r="E9" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="124"/>
-      <c r="G9" s="95">
+      <c r="F9" s="116"/>
+      <c r="G9" s="90">
         <v>46753</v>
       </c>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="97"/>
-      <c r="K9" s="127" t="s">
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="L9" s="128"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="128"/>
-      <c r="P9" s="128"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
-      <c r="S9" s="129"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="119"/>
       <c r="W9" s="1"/>
     </row>
-    <row r="10" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="101">
+      <c r="C10" s="103">
         <v>45434</v>
       </c>
-      <c r="D10" s="126"/>
-      <c r="E10" s="123" t="b">
+      <c r="D10" s="114"/>
+      <c r="E10" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F10" s="124"/>
-      <c r="G10" s="95">
+      <c r="F10" s="116"/>
+      <c r="G10" s="90">
         <v>46143</v>
       </c>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="97"/>
-      <c r="K10" s="127" t="s">
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="117" t="s">
         <v>158</v>
       </c>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
-      <c r="P10" s="128"/>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
-      <c r="S10" s="129"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="118"/>
+      <c r="O10" s="118"/>
+      <c r="P10" s="118"/>
+      <c r="Q10" s="118"/>
+      <c r="R10" s="118"/>
+      <c r="S10" s="119"/>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="101">
+      <c r="C11" s="103">
         <v>45616</v>
       </c>
-      <c r="D11" s="126"/>
-      <c r="E11" s="123" t="b">
+      <c r="D11" s="114"/>
+      <c r="E11" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F11" s="124"/>
-      <c r="G11" s="95">
+      <c r="F11" s="116"/>
+      <c r="G11" s="90">
         <v>46327</v>
       </c>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="127" t="s">
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="117" t="s">
         <v>159</v>
       </c>
-      <c r="L11" s="128"/>
-      <c r="M11" s="128"/>
-      <c r="N11" s="128"/>
-      <c r="O11" s="128"/>
-      <c r="P11" s="128"/>
-      <c r="Q11" s="128"/>
-      <c r="R11" s="128"/>
-      <c r="S11" s="129"/>
-    </row>
-    <row r="12" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="118"/>
+      <c r="M11" s="118"/>
+      <c r="N11" s="118"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="118"/>
+      <c r="Q11" s="118"/>
+      <c r="R11" s="118"/>
+      <c r="S11" s="119"/>
+    </row>
+    <row r="12" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="101">
+      <c r="C12" s="103">
         <v>45689</v>
       </c>
-      <c r="D12" s="126"/>
-      <c r="E12" s="123" t="b">
+      <c r="D12" s="114"/>
+      <c r="E12" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F12" s="124"/>
-      <c r="G12" s="95">
+      <c r="F12" s="116"/>
+      <c r="G12" s="90">
         <v>46419</v>
       </c>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="127" t="s">
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="117" t="s">
         <v>160</v>
       </c>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="128"/>
-      <c r="O12" s="128"/>
-      <c r="P12" s="128"/>
-      <c r="Q12" s="128"/>
-      <c r="R12" s="128"/>
-      <c r="S12" s="129"/>
-    </row>
-    <row r="13" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="119"/>
+    </row>
+    <row r="13" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="101">
+      <c r="C13" s="103">
         <v>45809</v>
       </c>
-      <c r="D13" s="126"/>
-      <c r="E13" s="123" t="b">
+      <c r="D13" s="114"/>
+      <c r="E13" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="95">
+      <c r="F13" s="116"/>
+      <c r="G13" s="90">
         <v>46539</v>
       </c>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="127" t="s">
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="117" t="s">
         <v>152</v>
       </c>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="129"/>
-    </row>
-    <row r="14" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="119"/>
+    </row>
+    <row r="14" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="101">
+      <c r="C14" s="103">
         <v>46023</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="123" t="b">
+      <c r="D14" s="114"/>
+      <c r="E14" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="124"/>
-      <c r="G14" s="95">
+      <c r="F14" s="116"/>
+      <c r="G14" s="90">
         <v>46753</v>
       </c>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="127" t="s">
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="L14" s="128"/>
-      <c r="M14" s="128"/>
-      <c r="N14" s="128"/>
-      <c r="O14" s="128"/>
-      <c r="P14" s="128"/>
-      <c r="Q14" s="128"/>
-      <c r="R14" s="128"/>
-      <c r="S14" s="129"/>
-    </row>
-    <row r="15" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="118"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="119"/>
+    </row>
+    <row r="15" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="123" t="b">
+      <c r="C15" s="120"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="124"/>
-      <c r="G15" s="95">
+      <c r="F15" s="116"/>
+      <c r="G15" s="90">
         <v>46143</v>
       </c>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="128"/>
-      <c r="M15" s="128"/>
-      <c r="N15" s="128"/>
-      <c r="O15" s="128"/>
-      <c r="P15" s="128"/>
-      <c r="Q15" s="128"/>
-      <c r="R15" s="128"/>
-      <c r="S15" s="129"/>
-    </row>
-    <row r="16" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="119"/>
+    </row>
+    <row r="16" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="121"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="123" t="b">
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="124"/>
-      <c r="G16" s="95">
+      <c r="F16" s="116"/>
+      <c r="G16" s="90">
         <v>46266</v>
       </c>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="128"/>
-      <c r="M16" s="128"/>
-      <c r="N16" s="128"/>
-      <c r="O16" s="128"/>
-      <c r="P16" s="128"/>
-      <c r="Q16" s="128"/>
-      <c r="R16" s="128"/>
-      <c r="S16" s="129"/>
-    </row>
-    <row r="17" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="119"/>
+    </row>
+    <row r="17" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="121"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="123" t="b">
+      <c r="C17" s="120"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="124" t="b">
+      <c r="F17" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G17" s="95">
+      <c r="G17" s="90">
         <v>46388</v>
       </c>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="128"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="128"/>
-      <c r="P17" s="128"/>
-      <c r="Q17" s="128"/>
-      <c r="R17" s="128"/>
-      <c r="S17" s="129"/>
-    </row>
-    <row r="18" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="118"/>
+      <c r="P17" s="118"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="119"/>
+    </row>
+    <row r="18" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="121"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="123" t="b">
+      <c r="C18" s="120"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="124" t="b">
+      <c r="F18" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="90">
         <v>46478</v>
       </c>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="127" t="s">
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="117" t="s">
         <v>215</v>
       </c>
-      <c r="L18" s="128"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="128"/>
-      <c r="O18" s="128"/>
-      <c r="P18" s="128"/>
-      <c r="Q18" s="128"/>
-      <c r="R18" s="128"/>
-      <c r="S18" s="129"/>
-    </row>
-    <row r="19" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="118"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="119"/>
+    </row>
+    <row r="19" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="121"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="123" t="b">
+      <c r="C19" s="120"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F19" s="124" t="b">
+      <c r="F19" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="95">
+      <c r="G19" s="90">
         <v>46539</v>
       </c>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="128"/>
-      <c r="O19" s="128"/>
-      <c r="P19" s="128"/>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="128"/>
-      <c r="S19" s="129"/>
-    </row>
-    <row r="20" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="118"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="119"/>
+    </row>
+    <row r="20" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="108"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="110" t="b">
+      <c r="C20" s="122"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="124" t="b">
         <v>0</v>
       </c>
-      <c r="F20" s="111" t="b">
+      <c r="F20" s="125" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="112">
+      <c r="G20" s="126">
         <v>46631</v>
       </c>
-      <c r="H20" s="113"/>
-      <c r="I20" s="113"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="116"/>
-      <c r="R20" s="116"/>
-      <c r="S20" s="117"/>
-    </row>
-    <row r="22" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:23" ht="21" x14ac:dyDescent="0.4">
-      <c r="B23" s="130" t="s">
+      <c r="H20" s="127"/>
+      <c r="I20" s="127"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="130"/>
+      <c r="M20" s="130"/>
+      <c r="N20" s="130"/>
+      <c r="O20" s="130"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="130"/>
+      <c r="R20" s="130"/>
+      <c r="S20" s="131"/>
+    </row>
+    <row r="22" spans="2:23" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:23" ht="22" x14ac:dyDescent="0.3">
+      <c r="B23" s="132" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="131"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="131"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="131"/>
-      <c r="L23" s="131"/>
-      <c r="M23" s="131"/>
-      <c r="N23" s="131"/>
-      <c r="O23" s="131"/>
-      <c r="P23" s="131"/>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
-      <c r="S23" s="132"/>
-    </row>
-    <row r="24" spans="2:23" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="133"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="133"/>
+      <c r="Q23" s="133"/>
+      <c r="R23" s="133"/>
+      <c r="S23" s="134"/>
+    </row>
+    <row r="24" spans="2:23" s="7" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B24" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="133" t="s">
+      <c r="C24" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135" t="s">
+      <c r="D24" s="107"/>
+      <c r="E24" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="136"/>
-      <c r="G24" s="137" t="s">
+      <c r="F24" s="109"/>
+      <c r="G24" s="110" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="138"/>
-      <c r="I24" s="138"/>
-      <c r="J24" s="139"/>
-      <c r="K24" s="98" t="s">
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="98"/>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="98"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="140"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="95"/>
+      <c r="P24" s="95"/>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="95"/>
+      <c r="S24" s="113"/>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="101">
+      <c r="C25" s="103">
         <v>45935</v>
       </c>
-      <c r="D25" s="126"/>
-      <c r="E25" s="123" t="b">
+      <c r="D25" s="114"/>
+      <c r="E25" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="124"/>
-      <c r="G25" s="95">
+      <c r="F25" s="116"/>
+      <c r="G25" s="90">
         <v>46296</v>
       </c>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="127" t="s">
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="117" t="s">
         <v>227</v>
       </c>
-      <c r="L25" s="128"/>
-      <c r="M25" s="128"/>
-      <c r="N25" s="128"/>
-      <c r="O25" s="128"/>
-      <c r="P25" s="128"/>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="128"/>
-      <c r="S25" s="129"/>
+      <c r="L25" s="118"/>
+      <c r="M25" s="118"/>
+      <c r="N25" s="118"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="118"/>
+      <c r="Q25" s="118"/>
+      <c r="R25" s="118"/>
+      <c r="S25" s="119"/>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B26" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="101">
+      <c r="C26" s="103">
         <v>45809</v>
       </c>
-      <c r="D26" s="126"/>
-      <c r="E26" s="123" t="b">
+      <c r="D26" s="114"/>
+      <c r="E26" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F26" s="124"/>
-      <c r="G26" s="95">
+      <c r="F26" s="116"/>
+      <c r="G26" s="90">
         <v>46174</v>
       </c>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="127"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="128"/>
-      <c r="N26" s="128"/>
-      <c r="O26" s="128"/>
-      <c r="P26" s="128"/>
-      <c r="Q26" s="128"/>
-      <c r="R26" s="128"/>
-      <c r="S26" s="129"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="118"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="118"/>
+      <c r="Q26" s="118"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="119"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B27" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="101">
+      <c r="C27" s="103">
         <v>46029</v>
       </c>
-      <c r="D27" s="126"/>
-      <c r="E27" s="123" t="b">
+      <c r="D27" s="114"/>
+      <c r="E27" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F27" s="124"/>
-      <c r="G27" s="95">
+      <c r="F27" s="116"/>
+      <c r="G27" s="90">
         <v>46388</v>
       </c>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="127" t="s">
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="L27" s="128"/>
-      <c r="M27" s="128"/>
-      <c r="N27" s="128"/>
-      <c r="O27" s="128"/>
-      <c r="P27" s="128"/>
-      <c r="Q27" s="128"/>
-      <c r="R27" s="128"/>
-      <c r="S27" s="129"/>
+      <c r="L27" s="118"/>
+      <c r="M27" s="118"/>
+      <c r="N27" s="118"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="118"/>
+      <c r="Q27" s="118"/>
+      <c r="R27" s="118"/>
+      <c r="S27" s="119"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B28" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="101">
+      <c r="C28" s="103">
         <v>45799</v>
       </c>
-      <c r="D28" s="126"/>
-      <c r="E28" s="123" t="b">
+      <c r="D28" s="114"/>
+      <c r="E28" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F28" s="124"/>
-      <c r="G28" s="95">
+      <c r="F28" s="116"/>
+      <c r="G28" s="90">
         <v>46143</v>
       </c>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="127" t="s">
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="117" t="s">
         <v>242</v>
       </c>
-      <c r="L28" s="128"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="128"/>
-      <c r="O28" s="128"/>
-      <c r="P28" s="128"/>
-      <c r="Q28" s="128"/>
-      <c r="R28" s="128"/>
-      <c r="S28" s="129"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="118"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="118"/>
+      <c r="P28" s="118"/>
+      <c r="Q28" s="118"/>
+      <c r="R28" s="118"/>
+      <c r="S28" s="119"/>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B29" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="101">
+      <c r="C29" s="103">
         <v>45981</v>
       </c>
-      <c r="D29" s="126"/>
-      <c r="E29" s="123" t="b">
+      <c r="D29" s="114"/>
+      <c r="E29" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F29" s="124"/>
-      <c r="G29" s="95">
+      <c r="F29" s="116"/>
+      <c r="G29" s="90">
         <v>46327</v>
       </c>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="127" t="s">
+      <c r="H29" s="91"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="117" t="s">
         <v>228</v>
       </c>
-      <c r="L29" s="128"/>
-      <c r="M29" s="128"/>
-      <c r="N29" s="128"/>
-      <c r="O29" s="128"/>
-      <c r="P29" s="128"/>
-      <c r="Q29" s="128"/>
-      <c r="R29" s="128"/>
-      <c r="S29" s="129"/>
-    </row>
-    <row r="30" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L29" s="118"/>
+      <c r="M29" s="118"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="118"/>
+      <c r="P29" s="118"/>
+      <c r="Q29" s="118"/>
+      <c r="R29" s="118"/>
+      <c r="S29" s="119"/>
+    </row>
+    <row r="30" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B30" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="101">
+      <c r="C30" s="103">
         <v>46054</v>
       </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="123" t="b">
+      <c r="D30" s="114"/>
+      <c r="E30" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F30" s="124"/>
-      <c r="G30" s="95">
+      <c r="F30" s="116"/>
+      <c r="G30" s="90">
         <v>46419</v>
       </c>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="127" t="s">
+      <c r="H30" s="91"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="L30" s="128"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="128"/>
-      <c r="O30" s="128"/>
-      <c r="P30" s="128"/>
-      <c r="Q30" s="128"/>
-      <c r="R30" s="128"/>
-      <c r="S30" s="129"/>
-    </row>
-    <row r="31" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L30" s="118"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="118"/>
+      <c r="Q30" s="118"/>
+      <c r="R30" s="118"/>
+      <c r="S30" s="119"/>
+    </row>
+    <row r="31" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B31" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="101">
+      <c r="C31" s="103">
         <v>45809</v>
       </c>
-      <c r="D31" s="126"/>
-      <c r="E31" s="123" t="b">
+      <c r="D31" s="114"/>
+      <c r="E31" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F31" s="124"/>
-      <c r="G31" s="95">
+      <c r="F31" s="116"/>
+      <c r="G31" s="90">
         <v>46174</v>
       </c>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="127" t="s">
+      <c r="H31" s="91"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="117" t="s">
         <v>152</v>
       </c>
-      <c r="L31" s="128"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="128"/>
-      <c r="O31" s="128"/>
-      <c r="P31" s="128"/>
-      <c r="Q31" s="128"/>
-      <c r="R31" s="128"/>
-      <c r="S31" s="129"/>
-    </row>
-    <row r="32" spans="2:23" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L31" s="118"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="118"/>
+      <c r="O31" s="118"/>
+      <c r="P31" s="118"/>
+      <c r="Q31" s="118"/>
+      <c r="R31" s="118"/>
+      <c r="S31" s="119"/>
+    </row>
+    <row r="32" spans="2:23" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B32" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="101">
+      <c r="C32" s="103">
         <v>46023</v>
       </c>
-      <c r="D32" s="126"/>
-      <c r="E32" s="123" t="b">
+      <c r="D32" s="114"/>
+      <c r="E32" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F32" s="124"/>
-      <c r="G32" s="95">
+      <c r="F32" s="116"/>
+      <c r="G32" s="90">
         <v>46388</v>
       </c>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="97"/>
-      <c r="K32" s="127" t="s">
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="128"/>
-      <c r="O32" s="128"/>
-      <c r="P32" s="128"/>
-      <c r="Q32" s="128"/>
-      <c r="R32" s="128"/>
-      <c r="S32" s="129"/>
-    </row>
-    <row r="33" spans="2:19" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L32" s="118"/>
+      <c r="M32" s="118"/>
+      <c r="N32" s="118"/>
+      <c r="O32" s="118"/>
+      <c r="P32" s="118"/>
+      <c r="Q32" s="118"/>
+      <c r="R32" s="118"/>
+      <c r="S32" s="119"/>
+    </row>
+    <row r="33" spans="2:19" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B33" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="101">
+      <c r="C33" s="103">
         <v>45782</v>
       </c>
-      <c r="D33" s="126"/>
-      <c r="E33" s="123" t="b">
+      <c r="D33" s="114"/>
+      <c r="E33" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F33" s="124"/>
-      <c r="G33" s="95">
+      <c r="F33" s="116"/>
+      <c r="G33" s="90">
         <v>46143</v>
       </c>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="141" t="s">
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="135" t="s">
         <v>204</v>
       </c>
-      <c r="L33" s="142"/>
-      <c r="M33" s="142"/>
-      <c r="N33" s="142"/>
-      <c r="O33" s="142"/>
-      <c r="P33" s="142"/>
-      <c r="Q33" s="142"/>
-      <c r="R33" s="142"/>
-      <c r="S33" s="143"/>
-    </row>
-    <row r="34" spans="2:19" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="136"/>
+      <c r="P33" s="136"/>
+      <c r="Q33" s="136"/>
+      <c r="R33" s="136"/>
+      <c r="S33" s="137"/>
+    </row>
+    <row r="34" spans="2:19" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B34" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="101">
+      <c r="C34" s="103">
         <v>45901</v>
       </c>
-      <c r="D34" s="126"/>
-      <c r="E34" s="123" t="b">
+      <c r="D34" s="114"/>
+      <c r="E34" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F34" s="124"/>
-      <c r="G34" s="95">
+      <c r="F34" s="116"/>
+      <c r="G34" s="90">
         <v>46266</v>
       </c>
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="97"/>
-      <c r="K34" s="127" t="s">
+      <c r="H34" s="91"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="117" t="s">
         <v>205</v>
       </c>
-      <c r="L34" s="128"/>
-      <c r="M34" s="128"/>
-      <c r="N34" s="128"/>
-      <c r="O34" s="128"/>
-      <c r="P34" s="128"/>
-      <c r="Q34" s="128"/>
-      <c r="R34" s="128"/>
-      <c r="S34" s="129"/>
-    </row>
-    <row r="35" spans="2:19" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L34" s="118"/>
+      <c r="M34" s="118"/>
+      <c r="N34" s="118"/>
+      <c r="O34" s="118"/>
+      <c r="P34" s="118"/>
+      <c r="Q34" s="118"/>
+      <c r="R34" s="118"/>
+      <c r="S34" s="119"/>
+    </row>
+    <row r="35" spans="2:19" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B35" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="101">
+      <c r="C35" s="103">
         <v>46023</v>
       </c>
-      <c r="D35" s="126"/>
-      <c r="E35" s="123" t="b">
+      <c r="D35" s="114"/>
+      <c r="E35" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F35" s="124" t="b">
+      <c r="F35" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G35" s="95">
+      <c r="G35" s="90">
         <v>46388</v>
       </c>
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="127" t="s">
+      <c r="H35" s="91"/>
+      <c r="I35" s="91"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="117" t="s">
         <v>223</v>
       </c>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="128"/>
-      <c r="O35" s="128"/>
-      <c r="P35" s="128"/>
-      <c r="Q35" s="128"/>
-      <c r="R35" s="128"/>
-      <c r="S35" s="129"/>
-    </row>
-    <row r="36" spans="2:19" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L35" s="118"/>
+      <c r="M35" s="118"/>
+      <c r="N35" s="118"/>
+      <c r="O35" s="118"/>
+      <c r="P35" s="118"/>
+      <c r="Q35" s="118"/>
+      <c r="R35" s="118"/>
+      <c r="S35" s="119"/>
+    </row>
+    <row r="36" spans="2:19" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B36" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="121">
+      <c r="C36" s="120">
         <v>46113</v>
       </c>
-      <c r="D36" s="122"/>
-      <c r="E36" s="123" t="b">
+      <c r="D36" s="121"/>
+      <c r="E36" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F36" s="124" t="b">
+      <c r="F36" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G36" s="95">
+      <c r="G36" s="90">
         <v>46478</v>
       </c>
-      <c r="H36" s="96"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="127" t="s">
+      <c r="H36" s="91"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="117" t="s">
         <v>231</v>
       </c>
-      <c r="L36" s="128"/>
-      <c r="M36" s="128"/>
-      <c r="N36" s="128"/>
-      <c r="O36" s="128"/>
-      <c r="P36" s="128"/>
-      <c r="Q36" s="128"/>
-      <c r="R36" s="128"/>
-      <c r="S36" s="129"/>
-    </row>
-    <row r="37" spans="2:19" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="L36" s="118"/>
+      <c r="M36" s="118"/>
+      <c r="N36" s="118"/>
+      <c r="O36" s="118"/>
+      <c r="P36" s="118"/>
+      <c r="Q36" s="118"/>
+      <c r="R36" s="118"/>
+      <c r="S36" s="119"/>
+    </row>
+    <row r="37" spans="2:19" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B37" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="121"/>
-      <c r="D37" s="122"/>
-      <c r="E37" s="123" t="b">
+      <c r="C37" s="120"/>
+      <c r="D37" s="121"/>
+      <c r="E37" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F37" s="124" t="b">
+      <c r="F37" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G37" s="95">
+      <c r="G37" s="90">
         <v>46143</v>
       </c>
-      <c r="H37" s="96"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="97"/>
-      <c r="K37" s="127" t="s">
+      <c r="H37" s="91"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="117" t="s">
         <v>234</v>
       </c>
-      <c r="L37" s="128"/>
-      <c r="M37" s="128"/>
-      <c r="N37" s="128"/>
-      <c r="O37" s="128"/>
-      <c r="P37" s="128"/>
-      <c r="Q37" s="128"/>
-      <c r="R37" s="128"/>
-      <c r="S37" s="129"/>
-    </row>
-    <row r="38" spans="2:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L37" s="118"/>
+      <c r="M37" s="118"/>
+      <c r="N37" s="118"/>
+      <c r="O37" s="118"/>
+      <c r="P37" s="118"/>
+      <c r="Q37" s="118"/>
+      <c r="R37" s="118"/>
+      <c r="S37" s="119"/>
+    </row>
+    <row r="38" spans="2:19" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B38" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="108"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="110" t="b">
+      <c r="C38" s="122"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="124" t="b">
         <v>0</v>
       </c>
-      <c r="F38" s="111" t="b">
+      <c r="F38" s="125" t="b">
         <v>0</v>
       </c>
-      <c r="G38" s="112">
+      <c r="G38" s="126">
         <v>46266</v>
       </c>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="114"/>
-      <c r="K38" s="115"/>
-      <c r="L38" s="116"/>
-      <c r="M38" s="116"/>
-      <c r="N38" s="116"/>
-      <c r="O38" s="116"/>
-      <c r="P38" s="116"/>
-      <c r="Q38" s="116"/>
-      <c r="R38" s="116"/>
-      <c r="S38" s="117"/>
-    </row>
-    <row r="40" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="2:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="B41" s="130" t="s">
+      <c r="H38" s="127"/>
+      <c r="I38" s="127"/>
+      <c r="J38" s="128"/>
+      <c r="K38" s="129"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130"/>
+      <c r="Q38" s="130"/>
+      <c r="R38" s="130"/>
+      <c r="S38" s="131"/>
+    </row>
+    <row r="40" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:19" ht="22" x14ac:dyDescent="0.3">
+      <c r="B41" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="131"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="131"/>
-      <c r="I41" s="131"/>
-      <c r="J41" s="131"/>
-      <c r="K41" s="131"/>
-      <c r="L41" s="131"/>
-      <c r="M41" s="131"/>
-      <c r="N41" s="131"/>
-      <c r="O41" s="131"/>
-      <c r="P41" s="131"/>
-      <c r="Q41" s="131"/>
-      <c r="R41" s="131"/>
-      <c r="S41" s="132"/>
-    </row>
-    <row r="42" spans="2:19" ht="18" x14ac:dyDescent="0.3">
+      <c r="C41" s="133"/>
+      <c r="D41" s="133"/>
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="133"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="133"/>
+      <c r="M41" s="133"/>
+      <c r="N41" s="133"/>
+      <c r="O41" s="133"/>
+      <c r="P41" s="133"/>
+      <c r="Q41" s="133"/>
+      <c r="R41" s="133"/>
+      <c r="S41" s="134"/>
+    </row>
+    <row r="42" spans="2:19" ht="19" x14ac:dyDescent="0.2">
       <c r="B42" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="133" t="s">
+      <c r="C42" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="134"/>
-      <c r="E42" s="135" t="s">
+      <c r="D42" s="107"/>
+      <c r="E42" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="F42" s="136"/>
-      <c r="G42" s="137" t="s">
+      <c r="F42" s="109"/>
+      <c r="G42" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="H42" s="138"/>
-      <c r="I42" s="138"/>
-      <c r="J42" s="139"/>
-      <c r="K42" s="98" t="s">
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
+      <c r="J42" s="112"/>
+      <c r="K42" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="L42" s="98"/>
-      <c r="M42" s="98"/>
-      <c r="N42" s="98"/>
-      <c r="O42" s="98"/>
-      <c r="P42" s="98"/>
-      <c r="Q42" s="98"/>
-      <c r="R42" s="98"/>
-      <c r="S42" s="140"/>
-    </row>
-    <row r="43" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L42" s="95"/>
+      <c r="M42" s="95"/>
+      <c r="N42" s="95"/>
+      <c r="O42" s="95"/>
+      <c r="P42" s="95"/>
+      <c r="Q42" s="95"/>
+      <c r="R42" s="95"/>
+      <c r="S42" s="113"/>
+    </row>
+    <row r="43" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B43" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="101">
+      <c r="C43" s="103">
         <v>45931</v>
       </c>
-      <c r="D43" s="126"/>
-      <c r="E43" s="123" t="b">
+      <c r="D43" s="114"/>
+      <c r="E43" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F43" s="124"/>
-      <c r="G43" s="95">
+      <c r="F43" s="116"/>
+      <c r="G43" s="90">
         <v>46661</v>
       </c>
-      <c r="H43" s="96"/>
-      <c r="I43" s="96"/>
-      <c r="J43" s="97"/>
-      <c r="K43" s="90" t="s">
+      <c r="H43" s="91"/>
+      <c r="I43" s="91"/>
+      <c r="J43" s="92"/>
+      <c r="K43" s="93" t="s">
         <v>227</v>
       </c>
-      <c r="L43" s="91"/>
-      <c r="M43" s="91"/>
-      <c r="N43" s="91"/>
-      <c r="O43" s="91"/>
-      <c r="P43" s="91"/>
-      <c r="Q43" s="91"/>
-      <c r="R43" s="91"/>
-      <c r="S43" s="125"/>
-    </row>
-    <row r="44" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L43" s="94"/>
+      <c r="M43" s="94"/>
+      <c r="N43" s="94"/>
+      <c r="O43" s="94"/>
+      <c r="P43" s="94"/>
+      <c r="Q43" s="94"/>
+      <c r="R43" s="94"/>
+      <c r="S43" s="138"/>
+    </row>
+    <row r="44" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B44" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="101">
+      <c r="C44" s="103">
         <v>45444</v>
       </c>
-      <c r="D44" s="126"/>
-      <c r="E44" s="123" t="b">
+      <c r="D44" s="114"/>
+      <c r="E44" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F44" s="124"/>
-      <c r="G44" s="95">
+      <c r="F44" s="116"/>
+      <c r="G44" s="90">
         <v>46174</v>
       </c>
-      <c r="H44" s="96"/>
-      <c r="I44" s="96"/>
-      <c r="J44" s="97"/>
-      <c r="K44" s="90"/>
-      <c r="L44" s="91"/>
-      <c r="M44" s="91"/>
-      <c r="N44" s="91"/>
-      <c r="O44" s="91"/>
-      <c r="P44" s="91"/>
-      <c r="Q44" s="91"/>
-      <c r="R44" s="91"/>
-      <c r="S44" s="125"/>
-    </row>
-    <row r="45" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H44" s="91"/>
+      <c r="I44" s="91"/>
+      <c r="J44" s="92"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="94"/>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="94"/>
+      <c r="S44" s="138"/>
+    </row>
+    <row r="45" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B45" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C45" s="101">
+      <c r="C45" s="103">
         <v>45658</v>
       </c>
-      <c r="D45" s="126"/>
-      <c r="E45" s="123" t="b">
+      <c r="D45" s="114"/>
+      <c r="E45" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F45" s="124"/>
-      <c r="G45" s="95">
+      <c r="F45" s="116"/>
+      <c r="G45" s="90">
         <v>46388</v>
       </c>
-      <c r="H45" s="96"/>
-      <c r="I45" s="96"/>
-      <c r="J45" s="97"/>
-      <c r="K45" s="90" t="s">
+      <c r="H45" s="91"/>
+      <c r="I45" s="91"/>
+      <c r="J45" s="92"/>
+      <c r="K45" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="L45" s="91"/>
-      <c r="M45" s="91"/>
-      <c r="N45" s="91"/>
-      <c r="O45" s="91"/>
-      <c r="P45" s="91"/>
-      <c r="Q45" s="91"/>
-      <c r="R45" s="91"/>
-      <c r="S45" s="125"/>
-    </row>
-    <row r="46" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L45" s="94"/>
+      <c r="M45" s="94"/>
+      <c r="N45" s="94"/>
+      <c r="O45" s="94"/>
+      <c r="P45" s="94"/>
+      <c r="Q45" s="94"/>
+      <c r="R45" s="94"/>
+      <c r="S45" s="138"/>
+    </row>
+    <row r="46" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B46" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="101">
+      <c r="C46" s="103">
         <v>45799</v>
       </c>
-      <c r="D46" s="126"/>
-      <c r="E46" s="123" t="b">
+      <c r="D46" s="114"/>
+      <c r="E46" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F46" s="124"/>
-      <c r="G46" s="95">
+      <c r="F46" s="116"/>
+      <c r="G46" s="90">
         <v>46508</v>
       </c>
-      <c r="H46" s="96"/>
-      <c r="I46" s="96"/>
-      <c r="J46" s="97"/>
-      <c r="K46" s="90"/>
-      <c r="L46" s="91"/>
-      <c r="M46" s="91"/>
-      <c r="N46" s="91"/>
-      <c r="O46" s="91"/>
-      <c r="P46" s="91"/>
-      <c r="Q46" s="91"/>
-      <c r="R46" s="91"/>
-      <c r="S46" s="125"/>
-    </row>
-    <row r="47" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H46" s="91"/>
+      <c r="I46" s="91"/>
+      <c r="J46" s="92"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="94"/>
+      <c r="M46" s="94"/>
+      <c r="N46" s="94"/>
+      <c r="O46" s="94"/>
+      <c r="P46" s="94"/>
+      <c r="Q46" s="94"/>
+      <c r="R46" s="94"/>
+      <c r="S46" s="138"/>
+    </row>
+    <row r="47" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B47" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="101">
+      <c r="C47" s="103">
         <v>45981</v>
       </c>
-      <c r="D47" s="126"/>
-      <c r="E47" s="123" t="b">
+      <c r="D47" s="114"/>
+      <c r="E47" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F47" s="124"/>
-      <c r="G47" s="95">
+      <c r="F47" s="116"/>
+      <c r="G47" s="90">
         <v>46692</v>
       </c>
-      <c r="H47" s="96"/>
-      <c r="I47" s="96"/>
-      <c r="J47" s="97"/>
-      <c r="K47" s="90"/>
-      <c r="L47" s="91"/>
-      <c r="M47" s="91"/>
-      <c r="N47" s="91"/>
-      <c r="O47" s="91"/>
-      <c r="P47" s="91"/>
-      <c r="Q47" s="91"/>
-      <c r="R47" s="91"/>
-      <c r="S47" s="125"/>
-    </row>
-    <row r="48" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H47" s="91"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="92"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="94"/>
+      <c r="M47" s="94"/>
+      <c r="N47" s="94"/>
+      <c r="O47" s="94"/>
+      <c r="P47" s="94"/>
+      <c r="Q47" s="94"/>
+      <c r="R47" s="94"/>
+      <c r="S47" s="138"/>
+    </row>
+    <row r="48" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B48" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="101">
+      <c r="C48" s="103">
         <v>46054</v>
       </c>
-      <c r="D48" s="126"/>
-      <c r="E48" s="123" t="b">
+      <c r="D48" s="114"/>
+      <c r="E48" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F48" s="124"/>
-      <c r="G48" s="95">
+      <c r="F48" s="116"/>
+      <c r="G48" s="90">
         <v>46784</v>
       </c>
-      <c r="H48" s="96"/>
-      <c r="I48" s="96"/>
-      <c r="J48" s="97"/>
-      <c r="K48" s="90" t="s">
+      <c r="H48" s="91"/>
+      <c r="I48" s="91"/>
+      <c r="J48" s="92"/>
+      <c r="K48" s="93" t="s">
         <v>229</v>
       </c>
-      <c r="L48" s="91"/>
-      <c r="M48" s="91"/>
-      <c r="N48" s="91"/>
-      <c r="O48" s="91"/>
-      <c r="P48" s="91"/>
-      <c r="Q48" s="91"/>
-      <c r="R48" s="91"/>
-      <c r="S48" s="125"/>
-    </row>
-    <row r="49" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L48" s="94"/>
+      <c r="M48" s="94"/>
+      <c r="N48" s="94"/>
+      <c r="O48" s="94"/>
+      <c r="P48" s="94"/>
+      <c r="Q48" s="94"/>
+      <c r="R48" s="94"/>
+      <c r="S48" s="138"/>
+    </row>
+    <row r="49" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B49" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="101">
+      <c r="C49" s="103">
         <v>45444</v>
       </c>
-      <c r="D49" s="126"/>
-      <c r="E49" s="123" t="b">
+      <c r="D49" s="114"/>
+      <c r="E49" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F49" s="124"/>
-      <c r="G49" s="95">
+      <c r="F49" s="116"/>
+      <c r="G49" s="90">
         <v>46174</v>
       </c>
-      <c r="H49" s="96"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="97"/>
-      <c r="K49" s="90"/>
-      <c r="L49" s="91"/>
-      <c r="M49" s="91"/>
-      <c r="N49" s="91"/>
-      <c r="O49" s="91"/>
-      <c r="P49" s="91"/>
-      <c r="Q49" s="91"/>
-      <c r="R49" s="91"/>
-      <c r="S49" s="125"/>
-    </row>
-    <row r="50" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H49" s="91"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="92"/>
+      <c r="K49" s="93"/>
+      <c r="L49" s="94"/>
+      <c r="M49" s="94"/>
+      <c r="N49" s="94"/>
+      <c r="O49" s="94"/>
+      <c r="P49" s="94"/>
+      <c r="Q49" s="94"/>
+      <c r="R49" s="94"/>
+      <c r="S49" s="138"/>
+    </row>
+    <row r="50" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B50" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="101">
+      <c r="C50" s="103">
         <v>45658</v>
       </c>
-      <c r="D50" s="126"/>
-      <c r="E50" s="123" t="b">
+      <c r="D50" s="114"/>
+      <c r="E50" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F50" s="124"/>
-      <c r="G50" s="95">
+      <c r="F50" s="116"/>
+      <c r="G50" s="90">
         <v>46388</v>
       </c>
-      <c r="H50" s="96"/>
-      <c r="I50" s="96"/>
-      <c r="J50" s="97"/>
-      <c r="K50" s="90"/>
-      <c r="L50" s="91"/>
-      <c r="M50" s="91"/>
-      <c r="N50" s="91"/>
-      <c r="O50" s="91"/>
-      <c r="P50" s="91"/>
-      <c r="Q50" s="91"/>
-      <c r="R50" s="91"/>
-      <c r="S50" s="125"/>
-    </row>
-    <row r="51" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H50" s="91"/>
+      <c r="I50" s="91"/>
+      <c r="J50" s="92"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="94"/>
+      <c r="M50" s="94"/>
+      <c r="N50" s="94"/>
+      <c r="O50" s="94"/>
+      <c r="P50" s="94"/>
+      <c r="Q50" s="94"/>
+      <c r="R50" s="94"/>
+      <c r="S50" s="138"/>
+    </row>
+    <row r="51" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B51" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="101">
+      <c r="C51" s="103">
         <v>45778</v>
       </c>
-      <c r="D51" s="126"/>
-      <c r="E51" s="123" t="b">
+      <c r="D51" s="114"/>
+      <c r="E51" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F51" s="124"/>
-      <c r="G51" s="95">
+      <c r="F51" s="116"/>
+      <c r="G51" s="90">
         <v>46508</v>
       </c>
-      <c r="H51" s="96"/>
-      <c r="I51" s="96"/>
-      <c r="J51" s="97"/>
-      <c r="K51" s="90"/>
-      <c r="L51" s="91"/>
-      <c r="M51" s="91"/>
-      <c r="N51" s="91"/>
-      <c r="O51" s="91"/>
-      <c r="P51" s="91"/>
-      <c r="Q51" s="91"/>
-      <c r="R51" s="91"/>
-      <c r="S51" s="125"/>
-    </row>
-    <row r="52" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H51" s="91"/>
+      <c r="I51" s="91"/>
+      <c r="J51" s="92"/>
+      <c r="K51" s="93"/>
+      <c r="L51" s="94"/>
+      <c r="M51" s="94"/>
+      <c r="N51" s="94"/>
+      <c r="O51" s="94"/>
+      <c r="P51" s="94"/>
+      <c r="Q51" s="94"/>
+      <c r="R51" s="94"/>
+      <c r="S51" s="138"/>
+    </row>
+    <row r="52" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B52" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C52" s="101">
+      <c r="C52" s="103">
         <v>45901</v>
       </c>
-      <c r="D52" s="126"/>
-      <c r="E52" s="123" t="b">
+      <c r="D52" s="114"/>
+      <c r="E52" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F52" s="124"/>
-      <c r="G52" s="95">
+      <c r="F52" s="116"/>
+      <c r="G52" s="90">
         <v>46631</v>
       </c>
-      <c r="H52" s="96"/>
-      <c r="I52" s="96"/>
-      <c r="J52" s="97"/>
-      <c r="K52" s="90" t="s">
+      <c r="H52" s="91"/>
+      <c r="I52" s="91"/>
+      <c r="J52" s="92"/>
+      <c r="K52" s="93" t="s">
         <v>205</v>
       </c>
-      <c r="L52" s="91"/>
-      <c r="M52" s="91"/>
-      <c r="N52" s="91"/>
-      <c r="O52" s="91"/>
-      <c r="P52" s="91"/>
-      <c r="Q52" s="91"/>
-      <c r="R52" s="91"/>
-      <c r="S52" s="125"/>
-    </row>
-    <row r="53" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L52" s="94"/>
+      <c r="M52" s="94"/>
+      <c r="N52" s="94"/>
+      <c r="O52" s="94"/>
+      <c r="P52" s="94"/>
+      <c r="Q52" s="94"/>
+      <c r="R52" s="94"/>
+      <c r="S52" s="138"/>
+    </row>
+    <row r="53" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B53" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="101">
+      <c r="C53" s="103">
         <v>46023</v>
       </c>
-      <c r="D53" s="126"/>
-      <c r="E53" s="123" t="b">
+      <c r="D53" s="114"/>
+      <c r="E53" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="F53" s="124" t="b">
+      <c r="F53" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G53" s="95">
+      <c r="G53" s="90">
         <v>46753</v>
       </c>
-      <c r="H53" s="96"/>
-      <c r="I53" s="96"/>
-      <c r="J53" s="97"/>
-      <c r="K53" s="90" t="s">
+      <c r="H53" s="91"/>
+      <c r="I53" s="91"/>
+      <c r="J53" s="92"/>
+      <c r="K53" s="93" t="s">
         <v>223</v>
       </c>
-      <c r="L53" s="91"/>
-      <c r="M53" s="91"/>
-      <c r="N53" s="91"/>
-      <c r="O53" s="91"/>
-      <c r="P53" s="91"/>
-      <c r="Q53" s="91"/>
-      <c r="R53" s="91"/>
-      <c r="S53" s="125"/>
-    </row>
-    <row r="54" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="L53" s="94"/>
+      <c r="M53" s="94"/>
+      <c r="N53" s="94"/>
+      <c r="O53" s="94"/>
+      <c r="P53" s="94"/>
+      <c r="Q53" s="94"/>
+      <c r="R53" s="94"/>
+      <c r="S53" s="138"/>
+    </row>
+    <row r="54" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B54" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="121"/>
-      <c r="D54" s="122"/>
-      <c r="E54" s="123" t="b">
+      <c r="C54" s="120"/>
+      <c r="D54" s="121"/>
+      <c r="E54" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F54" s="124" t="b">
+      <c r="F54" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G54" s="95">
+      <c r="G54" s="90">
         <v>46478</v>
       </c>
-      <c r="H54" s="96"/>
-      <c r="I54" s="96"/>
-      <c r="J54" s="97"/>
-      <c r="K54" s="90"/>
-      <c r="L54" s="91"/>
-      <c r="M54" s="91"/>
-      <c r="N54" s="91"/>
-      <c r="O54" s="91"/>
-      <c r="P54" s="91"/>
-      <c r="Q54" s="91"/>
-      <c r="R54" s="91"/>
-      <c r="S54" s="125"/>
-    </row>
-    <row r="55" spans="2:19" ht="21" x14ac:dyDescent="0.3">
+      <c r="H54" s="91"/>
+      <c r="I54" s="91"/>
+      <c r="J54" s="92"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="94"/>
+      <c r="M54" s="94"/>
+      <c r="N54" s="94"/>
+      <c r="O54" s="94"/>
+      <c r="P54" s="94"/>
+      <c r="Q54" s="94"/>
+      <c r="R54" s="94"/>
+      <c r="S54" s="138"/>
+    </row>
+    <row r="55" spans="2:19" ht="22" x14ac:dyDescent="0.2">
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="121"/>
-      <c r="D55" s="122"/>
-      <c r="E55" s="123" t="b">
+      <c r="C55" s="120"/>
+      <c r="D55" s="121"/>
+      <c r="E55" s="115" t="b">
         <v>0</v>
       </c>
-      <c r="F55" s="124" t="b">
+      <c r="F55" s="116" t="b">
         <v>0</v>
       </c>
-      <c r="G55" s="95">
+      <c r="G55" s="90">
         <v>46539</v>
       </c>
-      <c r="H55" s="96"/>
-      <c r="I55" s="96"/>
-      <c r="J55" s="97"/>
-      <c r="K55" s="90"/>
-      <c r="L55" s="91"/>
-      <c r="M55" s="91"/>
-      <c r="N55" s="91"/>
-      <c r="O55" s="91"/>
-      <c r="P55" s="91"/>
-      <c r="Q55" s="91"/>
-      <c r="R55" s="91"/>
-      <c r="S55" s="125"/>
-    </row>
-    <row r="56" spans="2:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="92"/>
+      <c r="K55" s="93"/>
+      <c r="L55" s="94"/>
+      <c r="M55" s="94"/>
+      <c r="N55" s="94"/>
+      <c r="O55" s="94"/>
+      <c r="P55" s="94"/>
+      <c r="Q55" s="94"/>
+      <c r="R55" s="94"/>
+      <c r="S55" s="138"/>
+    </row>
+    <row r="56" spans="2:19" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B56" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="108"/>
-      <c r="D56" s="109"/>
-      <c r="E56" s="110" t="b">
+      <c r="C56" s="122"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="124" t="b">
         <v>0</v>
       </c>
-      <c r="F56" s="111" t="b">
+      <c r="F56" s="125" t="b">
         <v>0</v>
       </c>
-      <c r="G56" s="112">
+      <c r="G56" s="126">
         <v>46631</v>
       </c>
-      <c r="H56" s="113"/>
-      <c r="I56" s="113"/>
-      <c r="J56" s="114"/>
-      <c r="K56" s="118"/>
-      <c r="L56" s="119"/>
-      <c r="M56" s="119"/>
-      <c r="N56" s="119"/>
-      <c r="O56" s="119"/>
-      <c r="P56" s="119"/>
-      <c r="Q56" s="119"/>
-      <c r="R56" s="119"/>
-      <c r="S56" s="120"/>
+      <c r="H56" s="127"/>
+      <c r="I56" s="127"/>
+      <c r="J56" s="128"/>
+      <c r="K56" s="139"/>
+      <c r="L56" s="140"/>
+      <c r="M56" s="140"/>
+      <c r="N56" s="140"/>
+      <c r="O56" s="140"/>
+      <c r="P56" s="140"/>
+      <c r="Q56" s="140"/>
+      <c r="R56" s="140"/>
+      <c r="S56" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="183">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="K6:S6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="K7:S7"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:S10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="K11:S11"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:S8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="K9:S9"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="K12:S12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:S13"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:S16"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K24:S24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:S17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:S18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:S20"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:S28"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:S25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:S26"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="K38:S38"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:J56"/>
+    <mergeCell ref="K56:S56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:J55"/>
+    <mergeCell ref="K55:S55"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:J53"/>
+    <mergeCell ref="K53:S53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="K54:S54"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="K51:S51"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="K36:S36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="K37:S37"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:S19"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="K35:S35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="K34:S34"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:S27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="K52:S52"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="K49:S49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="K50:S50"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="K47:S47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="K48:S48"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="K45:S45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="K46:S46"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="K43:S43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="K44:S44"/>
+    <mergeCell ref="B41:S41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="K42:S42"/>
     <mergeCell ref="B5:S5"/>
     <mergeCell ref="B23:S23"/>
     <mergeCell ref="C33:D33"/>
@@ -7771,95 +7799,76 @@
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="K32:S32"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="K43:S43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="K44:S44"/>
-    <mergeCell ref="B41:S41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="K42:S42"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="K47:S47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="K48:S48"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="K45:S45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G46:J46"/>
-    <mergeCell ref="K46:S46"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="K52:S52"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="K49:S49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="K50:S50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="K36:S36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="K37:S37"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:S19"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="K35:S35"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="K34:S34"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:S27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="K38:S38"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="K56:S56"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:J55"/>
-    <mergeCell ref="K55:S55"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="G53:J53"/>
-    <mergeCell ref="K53:S53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="K54:S54"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="K51:S51"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:S28"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:S25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:S26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:S16"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K24:S24"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:S17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:S18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:S20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="K12:S12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="K11:S11"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="K8:S8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="K9:S9"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="K6:S6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="K7:S7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:S10"/>
   </mergeCells>
   <conditionalFormatting sqref="G43:G56">
     <cfRule type="cellIs" dxfId="20" priority="16" stopIfTrue="1" operator="greaterThanOrEqual">
@@ -7901,6 +7910,9 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7908,485 +7920,505 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206507B2-DCF2-4AEA-856B-C9879EC0C44B}">
   <dimension ref="B3:W28"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="M3" s="73">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:23" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:23" s="7" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B13" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="149" t="s">
+      <c r="C13" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="149"/>
-      <c r="E13" s="150" t="s">
+      <c r="D13" s="151"/>
+      <c r="E13" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="150"/>
-      <c r="G13" s="151" t="s">
+      <c r="F13" s="152"/>
+      <c r="G13" s="153" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="151"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="151"/>
-      <c r="K13" s="149" t="s">
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
+      <c r="K13" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="149"/>
-      <c r="M13" s="149"/>
-      <c r="N13" s="149"/>
-      <c r="O13" s="149"/>
-      <c r="P13" s="149"/>
-      <c r="Q13" s="149"/>
-      <c r="R13" s="149"/>
-      <c r="S13" s="152"/>
+      <c r="L13" s="151"/>
+      <c r="M13" s="151"/>
+      <c r="N13" s="151"/>
+      <c r="O13" s="151"/>
+      <c r="P13" s="151"/>
+      <c r="Q13" s="151"/>
+      <c r="R13" s="151"/>
+      <c r="S13" s="154"/>
       <c r="W13" s="1"/>
     </row>
-    <row r="14" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="105">
+      <c r="C14" s="98">
         <v>45901</v>
       </c>
-      <c r="D14" s="106"/>
-      <c r="E14" s="94" t="b">
+      <c r="D14" s="99"/>
+      <c r="E14" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="94"/>
-      <c r="G14" s="95">
+      <c r="F14" s="89"/>
+      <c r="G14" s="90">
         <v>46266</v>
       </c>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="87"/>
-      <c r="O14" s="87"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="153"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="155"/>
+      <c r="L14" s="155"/>
+      <c r="M14" s="155"/>
+      <c r="N14" s="155"/>
+      <c r="O14" s="155"/>
+      <c r="P14" s="155"/>
+      <c r="Q14" s="155"/>
+      <c r="R14" s="155"/>
+      <c r="S14" s="156"/>
       <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="105">
+      <c r="C15" s="98">
         <v>45801</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="94" t="b">
+      <c r="D15" s="99"/>
+      <c r="E15" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="95">
+      <c r="F15" s="89"/>
+      <c r="G15" s="90">
         <v>46143</v>
       </c>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="154" t="s">
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="144" t="s">
         <v>243</v>
       </c>
-      <c r="L15" s="154"/>
-      <c r="M15" s="154"/>
-      <c r="N15" s="154"/>
-      <c r="O15" s="154"/>
-      <c r="P15" s="154"/>
-      <c r="Q15" s="154"/>
-      <c r="R15" s="154"/>
-      <c r="S15" s="155"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="145"/>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="105">
+      <c r="C16" s="98">
         <v>45979</v>
       </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="94" t="b">
+      <c r="D16" s="99"/>
+      <c r="E16" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="94"/>
-      <c r="G16" s="95">
+      <c r="F16" s="89"/>
+      <c r="G16" s="90">
         <v>46327</v>
       </c>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="154" t="s">
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="L16" s="154"/>
-      <c r="M16" s="154"/>
-      <c r="N16" s="154"/>
-      <c r="O16" s="154"/>
-      <c r="P16" s="154"/>
-      <c r="Q16" s="154"/>
-      <c r="R16" s="154"/>
-      <c r="S16" s="155"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="144"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="145"/>
       <c r="W16" s="1"/>
     </row>
-    <row r="17" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="105">
+      <c r="C17" s="98">
         <v>45829</v>
       </c>
-      <c r="D17" s="106"/>
-      <c r="E17" s="94" t="b">
+      <c r="D17" s="99"/>
+      <c r="E17" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="95">
+      <c r="F17" s="89"/>
+      <c r="G17" s="90">
         <v>46194</v>
       </c>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="154" t="s">
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="144" t="s">
         <v>241</v>
       </c>
-      <c r="L17" s="154"/>
-      <c r="M17" s="154"/>
-      <c r="N17" s="154"/>
-      <c r="O17" s="154"/>
-      <c r="P17" s="154"/>
-      <c r="Q17" s="154"/>
-      <c r="R17" s="154"/>
-      <c r="S17" s="155"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="144"/>
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="145"/>
       <c r="W17" s="1"/>
     </row>
-    <row r="18" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="105">
+      <c r="C18" s="98">
         <v>45979</v>
       </c>
-      <c r="D18" s="106"/>
-      <c r="E18" s="94" t="b">
+      <c r="D18" s="99"/>
+      <c r="E18" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="94"/>
-      <c r="G18" s="95">
+      <c r="F18" s="89"/>
+      <c r="G18" s="90">
         <v>46327</v>
       </c>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="154" t="s">
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="144" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="154"/>
-      <c r="M18" s="154"/>
-      <c r="N18" s="154"/>
-      <c r="O18" s="154"/>
-      <c r="P18" s="154"/>
-      <c r="Q18" s="154"/>
-      <c r="R18" s="154"/>
-      <c r="S18" s="155"/>
-    </row>
-    <row r="19" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="144"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="144"/>
+      <c r="P18" s="144"/>
+      <c r="Q18" s="144"/>
+      <c r="R18" s="144"/>
+      <c r="S18" s="145"/>
+    </row>
+    <row r="19" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="105">
+      <c r="C19" s="98">
         <v>46054</v>
       </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="94" t="b">
+      <c r="D19" s="99"/>
+      <c r="E19" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="95">
+      <c r="F19" s="89"/>
+      <c r="G19" s="90">
         <v>46419</v>
       </c>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="154" t="s">
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="144" t="s">
         <v>211</v>
       </c>
-      <c r="L19" s="154"/>
-      <c r="M19" s="154"/>
-      <c r="N19" s="154"/>
-      <c r="O19" s="154"/>
-      <c r="P19" s="154"/>
-      <c r="Q19" s="154"/>
-      <c r="R19" s="154"/>
-      <c r="S19" s="155"/>
-    </row>
-    <row r="20" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="144"/>
+      <c r="M19" s="144"/>
+      <c r="N19" s="144"/>
+      <c r="O19" s="144"/>
+      <c r="P19" s="144"/>
+      <c r="Q19" s="144"/>
+      <c r="R19" s="144"/>
+      <c r="S19" s="145"/>
+    </row>
+    <row r="20" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="105">
+      <c r="C20" s="98">
         <v>45809</v>
       </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="94" t="b">
+      <c r="D20" s="99"/>
+      <c r="E20" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="95">
+      <c r="F20" s="89"/>
+      <c r="G20" s="90">
         <v>46174</v>
       </c>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="154" t="s">
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="144" t="s">
         <v>241</v>
       </c>
-      <c r="L20" s="154"/>
-      <c r="M20" s="154"/>
-      <c r="N20" s="154"/>
-      <c r="O20" s="154"/>
-      <c r="P20" s="154"/>
-      <c r="Q20" s="154"/>
-      <c r="R20" s="154"/>
-      <c r="S20" s="155"/>
-    </row>
-    <row r="21" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="144"/>
+      <c r="M20" s="144"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="144"/>
+      <c r="P20" s="144"/>
+      <c r="Q20" s="144"/>
+      <c r="R20" s="144"/>
+      <c r="S20" s="145"/>
+    </row>
+    <row r="21" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="105">
+      <c r="C21" s="98">
         <v>45992</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="94" t="b">
+      <c r="D21" s="99"/>
+      <c r="E21" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="94"/>
-      <c r="G21" s="95">
+      <c r="F21" s="89"/>
+      <c r="G21" s="90">
         <v>46357</v>
       </c>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="154" t="s">
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="L21" s="154"/>
-      <c r="M21" s="154"/>
-      <c r="N21" s="154"/>
-      <c r="O21" s="154"/>
-      <c r="P21" s="154"/>
-      <c r="Q21" s="154"/>
-      <c r="R21" s="154"/>
-      <c r="S21" s="155"/>
-    </row>
-    <row r="22" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="144"/>
+      <c r="S21" s="145"/>
+    </row>
+    <row r="22" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="105">
+      <c r="C22" s="98">
         <v>45778</v>
       </c>
-      <c r="D22" s="106"/>
-      <c r="E22" s="94" t="b">
+      <c r="D22" s="99"/>
+      <c r="E22" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F22" s="94"/>
-      <c r="G22" s="95">
+      <c r="F22" s="89"/>
+      <c r="G22" s="90">
         <v>46143</v>
       </c>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="154" t="s">
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="144" t="s">
         <v>243</v>
       </c>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="154"/>
-      <c r="O22" s="154"/>
-      <c r="P22" s="154"/>
-      <c r="Q22" s="154"/>
-      <c r="R22" s="154"/>
-      <c r="S22" s="155"/>
-    </row>
-    <row r="23" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="144"/>
+      <c r="M22" s="144"/>
+      <c r="N22" s="144"/>
+      <c r="O22" s="144"/>
+      <c r="P22" s="144"/>
+      <c r="Q22" s="144"/>
+      <c r="R22" s="144"/>
+      <c r="S22" s="145"/>
+    </row>
+    <row r="23" spans="2:23" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="105">
+      <c r="C23" s="98">
         <v>45901</v>
       </c>
-      <c r="D23" s="106"/>
-      <c r="E23" s="94" t="b">
+      <c r="D23" s="99"/>
+      <c r="E23" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="95">
+      <c r="F23" s="89"/>
+      <c r="G23" s="90">
         <v>46266</v>
       </c>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="154" t="s">
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="L23" s="154"/>
-      <c r="M23" s="154"/>
-      <c r="N23" s="154"/>
-      <c r="O23" s="154"/>
-      <c r="P23" s="154"/>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="154"/>
-      <c r="S23" s="155"/>
-    </row>
-    <row r="24" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L23" s="144"/>
+      <c r="M23" s="144"/>
+      <c r="N23" s="144"/>
+      <c r="O23" s="144"/>
+      <c r="P23" s="144"/>
+      <c r="Q23" s="144"/>
+      <c r="R23" s="144"/>
+      <c r="S23" s="145"/>
+    </row>
+    <row r="24" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B24" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="105">
+      <c r="C24" s="98">
         <v>46023</v>
       </c>
-      <c r="D24" s="106"/>
-      <c r="E24" s="94" t="b">
+      <c r="D24" s="99"/>
+      <c r="E24" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F24" s="94"/>
-      <c r="G24" s="95">
+      <c r="F24" s="89"/>
+      <c r="G24" s="90">
         <v>46388</v>
       </c>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="154" t="s">
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="144" t="s">
         <v>167</v>
       </c>
-      <c r="L24" s="154"/>
-      <c r="M24" s="154"/>
-      <c r="N24" s="154"/>
-      <c r="O24" s="154"/>
-      <c r="P24" s="154"/>
-      <c r="Q24" s="154"/>
-      <c r="R24" s="154"/>
-      <c r="S24" s="155"/>
-    </row>
-    <row r="25" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L24" s="144"/>
+      <c r="M24" s="144"/>
+      <c r="N24" s="144"/>
+      <c r="O24" s="144"/>
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="145"/>
+    </row>
+    <row r="25" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B25" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="105">
+      <c r="C25" s="98">
         <v>46082</v>
       </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="94" t="b">
+      <c r="D25" s="99"/>
+      <c r="E25" s="89" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="94"/>
-      <c r="G25" s="95">
+      <c r="F25" s="89"/>
+      <c r="G25" s="90">
         <v>46447</v>
       </c>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="154" t="s">
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="144" t="s">
         <v>214</v>
       </c>
-      <c r="L25" s="154"/>
-      <c r="M25" s="154"/>
-      <c r="N25" s="154"/>
-      <c r="O25" s="154"/>
-      <c r="P25" s="154"/>
-      <c r="Q25" s="154"/>
-      <c r="R25" s="154"/>
-      <c r="S25" s="155"/>
-    </row>
-    <row r="26" spans="2:23" ht="21" x14ac:dyDescent="0.3">
+      <c r="L25" s="144"/>
+      <c r="M25" s="144"/>
+      <c r="N25" s="144"/>
+      <c r="O25" s="144"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="145"/>
+    </row>
+    <row r="26" spans="2:23" ht="22" x14ac:dyDescent="0.2">
       <c r="B26" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="156"/>
-      <c r="D26" s="157"/>
-      <c r="E26" s="94" t="b">
+      <c r="C26" s="142"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="F26" s="94"/>
-      <c r="G26" s="95">
+      <c r="F26" s="89"/>
+      <c r="G26" s="90">
         <v>46174</v>
       </c>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="154" t="s">
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="144" t="s">
         <v>240</v>
       </c>
-      <c r="L26" s="154"/>
-      <c r="M26" s="154"/>
-      <c r="N26" s="154"/>
-      <c r="O26" s="154"/>
-      <c r="P26" s="154"/>
-      <c r="Q26" s="154"/>
-      <c r="R26" s="154"/>
-      <c r="S26" s="155"/>
-    </row>
-    <row r="27" spans="2:23" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="144"/>
+      <c r="M26" s="144"/>
+      <c r="N26" s="144"/>
+      <c r="O26" s="144"/>
+      <c r="P26" s="144"/>
+      <c r="Q26" s="144"/>
+      <c r="R26" s="144"/>
+      <c r="S26" s="145"/>
+    </row>
+    <row r="27" spans="2:23" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="144"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="146" t="b">
+      <c r="C27" s="146"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="148" t="b">
         <v>0</v>
       </c>
-      <c r="F27" s="146"/>
-      <c r="G27" s="112">
+      <c r="F27" s="148"/>
+      <c r="G27" s="126">
         <v>46296</v>
       </c>
-      <c r="H27" s="113"/>
-      <c r="I27" s="113"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="147"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="147"/>
-      <c r="P27" s="147"/>
-      <c r="Q27" s="147"/>
-      <c r="R27" s="147"/>
-      <c r="S27" s="148"/>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="H27" s="127"/>
+      <c r="I27" s="127"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="149"/>
+      <c r="L27" s="149"/>
+      <c r="M27" s="149"/>
+      <c r="N27" s="149"/>
+      <c r="O27" s="149"/>
+      <c r="P27" s="149"/>
+      <c r="Q27" s="149"/>
+      <c r="R27" s="149"/>
+      <c r="S27" s="150"/>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="J28" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:S26"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K24:S24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:S25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:S27"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:S16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:S17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:S18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:S19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:J20"/>
@@ -8403,38 +8435,18 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="K22:S22"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:S18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:S19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:S16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:S17"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:S27"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:S13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:S26"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K24:S24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:S25"/>
   </mergeCells>
   <conditionalFormatting sqref="G14:G27">
     <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="greaterThanOrEqual">
@@ -8457,6 +8469,9 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8464,26 +8479,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84841928-340E-42EF-8D1C-576163713E19}">
   <dimension ref="B2:F18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:6" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="158" t="s">
+    <row r="2" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:6" ht="25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="157" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="159"/>
+      <c r="C3" s="158"/>
       <c r="F3" s="73">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="66" t="s">
         <v>133</v>
       </c>
@@ -8492,7 +8507,7 @@
       </c>
       <c r="D4" s="45"/>
     </row>
-    <row r="5" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B5" s="28" t="s">
         <v>74</v>
       </c>
@@ -8501,7 +8516,7 @@
       </c>
       <c r="D5" s="29"/>
     </row>
-    <row r="6" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B6" s="30" t="s">
         <v>75</v>
       </c>
@@ -8509,7 +8524,7 @@
         <v>46753</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B7" s="78" t="s">
         <v>76</v>
       </c>
@@ -8517,7 +8532,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B8" s="30" t="s">
         <v>77</v>
       </c>
@@ -8525,7 +8540,7 @@
         <v>46661</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B9" s="30" t="s">
         <v>78</v>
       </c>
@@ -8533,7 +8548,7 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B10" s="30" t="s">
         <v>79</v>
       </c>
@@ -8541,7 +8556,7 @@
         <v>46569</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B11" s="30" t="s">
         <v>80</v>
       </c>
@@ -8549,7 +8564,7 @@
         <v>46569</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B12" s="30" t="s">
         <v>81</v>
       </c>
@@ -8557,7 +8572,7 @@
         <v>46447</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B13" s="78" t="s">
         <v>134</v>
       </c>
@@ -8565,7 +8580,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B14" s="30" t="s">
         <v>83</v>
       </c>
@@ -8573,7 +8588,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B15" s="30" t="s">
         <v>84</v>
       </c>
@@ -8581,7 +8596,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="19" x14ac:dyDescent="0.2">
       <c r="B16" s="30" t="s">
         <v>85</v>
       </c>
@@ -8589,7 +8604,7 @@
         <v>46447</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="19" x14ac:dyDescent="0.2">
       <c r="B17" s="30" t="s">
         <v>86</v>
       </c>
@@ -8597,7 +8612,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
         <v>136</v>
       </c>
@@ -8622,35 +8637,38 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34CD561-5272-447E-9A0C-45761C79ADD3}">
   <dimension ref="B2:I8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I2" s="73">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="158" t="s">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="157" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="159"/>
-    </row>
-    <row r="4" spans="2:9" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="158"/>
+    </row>
+    <row r="4" spans="2:9" ht="44.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="66" t="s">
         <v>133</v>
       </c>
@@ -8664,7 +8682,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9" ht="19" x14ac:dyDescent="0.25">
       <c r="B5" s="72" t="s">
         <v>80</v>
       </c>
@@ -8678,7 +8696,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:9" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="72" t="s">
         <v>84</v>
       </c>
@@ -8692,7 +8710,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="19" x14ac:dyDescent="0.25">
       <c r="B7" s="72" t="s">
         <v>85</v>
       </c>
@@ -8706,7 +8724,7 @@
         <v>46478</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:9" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="59" t="s">
         <v>136</v>
       </c>
@@ -8736,84 +8754,87 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD4CD05-5D21-457E-8543-484C2B11A481}">
   <dimension ref="B1:T55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.5" customWidth="1"/>
     <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" customWidth="1"/>
+    <col min="11" max="11" width="20.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
     <col min="13" max="13" width="16.6640625" customWidth="1"/>
     <col min="14" max="14" width="16.33203125" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="179" t="s">
+    <row r="1" spans="2:20" ht="34.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="192" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="180"/>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="180"/>
-      <c r="R1" s="180"/>
-      <c r="S1" s="180"/>
-      <c r="T1" s="181"/>
-    </row>
-    <row r="2" spans="2:20" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="158" t="s">
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="194"/>
+    </row>
+    <row r="2" spans="2:20" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="157" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
-      <c r="M2" s="160"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="160"/>
-      <c r="Q2" s="160"/>
-      <c r="R2" s="160"/>
-      <c r="S2" s="160"/>
-      <c r="T2" s="159"/>
-    </row>
-    <row r="3" spans="2:20" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="159"/>
+      <c r="T2" s="158"/>
+    </row>
+    <row r="3" spans="2:20" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="165" t="s">
+      <c r="C3" s="195" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="165"/>
+      <c r="D3" s="195"/>
       <c r="E3" s="54" t="s">
         <v>162</v>
       </c>
@@ -8844,23 +8865,23 @@
       <c r="N3" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="195" t="s">
         <v>91</v>
       </c>
-      <c r="P3" s="165"/>
-      <c r="Q3" s="165"/>
-      <c r="R3" s="165"/>
-      <c r="S3" s="165"/>
-      <c r="T3" s="166"/>
-    </row>
-    <row r="4" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="195"/>
+      <c r="T3" s="196"/>
+    </row>
+    <row r="4" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B4" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="167">
+      <c r="C4" s="197">
         <v>44470</v>
       </c>
-      <c r="D4" s="168"/>
+      <c r="D4" s="198"/>
       <c r="E4" s="43">
         <v>46660</v>
       </c>
@@ -8891,23 +8912,23 @@
       <c r="N4" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O4" s="169" t="s">
+      <c r="O4" s="199" t="s">
         <v>116</v>
       </c>
-      <c r="P4" s="170"/>
-      <c r="Q4" s="170"/>
-      <c r="R4" s="170"/>
-      <c r="S4" s="170"/>
-      <c r="T4" s="171"/>
-    </row>
-    <row r="5" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P4" s="200"/>
+      <c r="Q4" s="200"/>
+      <c r="R4" s="200"/>
+      <c r="S4" s="200"/>
+      <c r="T4" s="201"/>
+    </row>
+    <row r="5" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B5" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="167">
+      <c r="C5" s="197">
         <v>44805</v>
       </c>
-      <c r="D5" s="168"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="43">
         <v>46265</v>
       </c>
@@ -8938,23 +8959,23 @@
       <c r="N5" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O5" s="169" t="s">
+      <c r="O5" s="199" t="s">
         <v>116</v>
       </c>
-      <c r="P5" s="170"/>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="170"/>
-      <c r="S5" s="170"/>
-      <c r="T5" s="171"/>
-    </row>
-    <row r="6" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P5" s="200"/>
+      <c r="Q5" s="200"/>
+      <c r="R5" s="200"/>
+      <c r="S5" s="200"/>
+      <c r="T5" s="201"/>
+    </row>
+    <row r="6" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B6" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="162">
+      <c r="C6" s="166">
         <v>45323</v>
       </c>
-      <c r="D6" s="163"/>
+      <c r="D6" s="167"/>
       <c r="E6" s="43">
         <v>46053</v>
       </c>
@@ -8985,23 +9006,23 @@
       <c r="N6" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O6" s="88" t="s">
+      <c r="O6" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
-      <c r="S6" s="88"/>
-      <c r="T6" s="164"/>
-    </row>
-    <row r="7" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P6" s="170"/>
+      <c r="Q6" s="170"/>
+      <c r="R6" s="170"/>
+      <c r="S6" s="170"/>
+      <c r="T6" s="171"/>
+    </row>
+    <row r="7" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B7" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="167">
+      <c r="C7" s="197">
         <v>45474</v>
       </c>
-      <c r="D7" s="168"/>
+      <c r="D7" s="198"/>
       <c r="E7" s="43">
         <v>46203</v>
       </c>
@@ -9032,23 +9053,23 @@
       <c r="N7" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="O7" s="169" t="s">
+      <c r="O7" s="199" t="s">
         <v>116</v>
       </c>
-      <c r="P7" s="170"/>
-      <c r="Q7" s="170"/>
-      <c r="R7" s="170"/>
-      <c r="S7" s="170"/>
-      <c r="T7" s="171"/>
-    </row>
-    <row r="8" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P7" s="200"/>
+      <c r="Q7" s="200"/>
+      <c r="R7" s="200"/>
+      <c r="S7" s="200"/>
+      <c r="T7" s="201"/>
+    </row>
+    <row r="8" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B8" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="167">
+      <c r="C8" s="197">
         <v>44866</v>
       </c>
-      <c r="D8" s="168"/>
+      <c r="D8" s="198"/>
       <c r="E8" s="43">
         <v>46326</v>
       </c>
@@ -9079,23 +9100,23 @@
       <c r="N8" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O8" s="169" t="s">
+      <c r="O8" s="199" t="s">
         <v>116</v>
       </c>
-      <c r="P8" s="170"/>
-      <c r="Q8" s="170"/>
-      <c r="R8" s="170"/>
-      <c r="S8" s="170"/>
-      <c r="T8" s="171"/>
-    </row>
-    <row r="9" spans="2:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P8" s="200"/>
+      <c r="Q8" s="200"/>
+      <c r="R8" s="200"/>
+      <c r="S8" s="200"/>
+      <c r="T8" s="201"/>
+    </row>
+    <row r="9" spans="2:20" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="167">
+      <c r="C9" s="197">
         <v>44986</v>
       </c>
-      <c r="D9" s="168"/>
+      <c r="D9" s="198"/>
       <c r="E9" s="43">
         <v>46446</v>
       </c>
@@ -9126,23 +9147,23 @@
       <c r="N9" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O9" s="169" t="s">
+      <c r="O9" s="199" t="s">
         <v>116</v>
       </c>
-      <c r="P9" s="170"/>
-      <c r="Q9" s="170"/>
-      <c r="R9" s="170"/>
-      <c r="S9" s="170"/>
-      <c r="T9" s="171"/>
-    </row>
-    <row r="10" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P9" s="200"/>
+      <c r="Q9" s="200"/>
+      <c r="R9" s="200"/>
+      <c r="S9" s="200"/>
+      <c r="T9" s="201"/>
+    </row>
+    <row r="10" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B10" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="162">
+      <c r="C10" s="166">
         <v>45108</v>
       </c>
-      <c r="D10" s="163"/>
+      <c r="D10" s="167"/>
       <c r="E10" s="43">
         <v>46568</v>
       </c>
@@ -9173,23 +9194,23 @@
       <c r="N10" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="O10" s="88" t="s">
+      <c r="O10" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
-      <c r="R10" s="88"/>
-      <c r="S10" s="88"/>
-      <c r="T10" s="164"/>
-    </row>
-    <row r="11" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P10" s="170"/>
+      <c r="Q10" s="170"/>
+      <c r="R10" s="170"/>
+      <c r="S10" s="170"/>
+      <c r="T10" s="171"/>
+    </row>
+    <row r="11" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B11" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="162">
+      <c r="C11" s="166">
         <v>45323</v>
       </c>
-      <c r="D11" s="163"/>
+      <c r="D11" s="167"/>
       <c r="E11" s="43">
         <v>46053</v>
       </c>
@@ -9220,23 +9241,23 @@
       <c r="N11" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O11" s="88" t="s">
+      <c r="O11" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="164"/>
-    </row>
-    <row r="12" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P11" s="170"/>
+      <c r="Q11" s="170"/>
+      <c r="R11" s="170"/>
+      <c r="S11" s="170"/>
+      <c r="T11" s="171"/>
+    </row>
+    <row r="12" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B12" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="162">
+      <c r="C12" s="166">
         <v>45444</v>
       </c>
-      <c r="D12" s="163"/>
+      <c r="D12" s="167"/>
       <c r="E12" s="43">
         <v>46173</v>
       </c>
@@ -9267,23 +9288,23 @@
       <c r="N12" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="O12" s="88" t="s">
+      <c r="O12" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="P12" s="88"/>
-      <c r="Q12" s="88"/>
-      <c r="R12" s="88"/>
-      <c r="S12" s="88"/>
-      <c r="T12" s="164"/>
-    </row>
-    <row r="13" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P12" s="170"/>
+      <c r="Q12" s="170"/>
+      <c r="R12" s="170"/>
+      <c r="S12" s="170"/>
+      <c r="T12" s="171"/>
+    </row>
+    <row r="13" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B13" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="162">
+      <c r="C13" s="166">
         <v>45566</v>
       </c>
-      <c r="D13" s="163"/>
+      <c r="D13" s="167"/>
       <c r="E13" s="43">
         <v>46295</v>
       </c>
@@ -9314,23 +9335,23 @@
       <c r="N13" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O13" s="88" t="s">
+      <c r="O13" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="P13" s="88"/>
-      <c r="Q13" s="88"/>
-      <c r="R13" s="88"/>
-      <c r="S13" s="88"/>
-      <c r="T13" s="164"/>
-    </row>
-    <row r="14" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P13" s="170"/>
+      <c r="Q13" s="170"/>
+      <c r="R13" s="170"/>
+      <c r="S13" s="170"/>
+      <c r="T13" s="171"/>
+    </row>
+    <row r="14" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B14" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="162">
+      <c r="C14" s="166">
         <v>45689</v>
       </c>
-      <c r="D14" s="163"/>
+      <c r="D14" s="167"/>
       <c r="E14" s="43">
         <v>46418</v>
       </c>
@@ -9361,21 +9382,21 @@
       <c r="N14" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O14" s="88"/>
-      <c r="P14" s="88"/>
-      <c r="Q14" s="88"/>
-      <c r="R14" s="88"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="164"/>
-    </row>
-    <row r="15" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="O14" s="170"/>
+      <c r="P14" s="170"/>
+      <c r="Q14" s="170"/>
+      <c r="R14" s="170"/>
+      <c r="S14" s="170"/>
+      <c r="T14" s="171"/>
+    </row>
+    <row r="15" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B15" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="162">
+      <c r="C15" s="166">
         <v>45748</v>
       </c>
-      <c r="D15" s="163"/>
+      <c r="D15" s="167"/>
       <c r="E15" s="43">
         <v>46477</v>
       </c>
@@ -9406,21 +9427,21 @@
       <c r="N15" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O15" s="88"/>
-      <c r="P15" s="88"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="164"/>
-    </row>
-    <row r="16" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="O15" s="170"/>
+      <c r="P15" s="170"/>
+      <c r="Q15" s="170"/>
+      <c r="R15" s="170"/>
+      <c r="S15" s="170"/>
+      <c r="T15" s="171"/>
+    </row>
+    <row r="16" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B16" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="162">
+      <c r="C16" s="166">
         <v>45839</v>
       </c>
-      <c r="D16" s="163"/>
+      <c r="D16" s="167"/>
       <c r="E16" s="43">
         <v>46568</v>
       </c>
@@ -9451,21 +9472,21 @@
       <c r="N16" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="O16" s="88"/>
-      <c r="P16" s="88"/>
-      <c r="Q16" s="88"/>
-      <c r="R16" s="88"/>
-      <c r="S16" s="88"/>
-      <c r="T16" s="164"/>
-    </row>
-    <row r="17" spans="2:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O16" s="170"/>
+      <c r="P16" s="170"/>
+      <c r="Q16" s="170"/>
+      <c r="R16" s="170"/>
+      <c r="S16" s="170"/>
+      <c r="T16" s="171"/>
+    </row>
+    <row r="17" spans="2:20" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="172">
+      <c r="C17" s="178">
         <v>45962</v>
       </c>
-      <c r="D17" s="173"/>
+      <c r="D17" s="179"/>
       <c r="E17" s="48">
         <v>46691</v>
       </c>
@@ -9496,14 +9517,14 @@
       <c r="N17" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="O17" s="174"/>
-      <c r="P17" s="174"/>
-      <c r="Q17" s="174"/>
-      <c r="R17" s="174"/>
-      <c r="S17" s="174"/>
-      <c r="T17" s="175"/>
-    </row>
-    <row r="18" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="O17" s="180"/>
+      <c r="P17" s="180"/>
+      <c r="Q17" s="180"/>
+      <c r="R17" s="180"/>
+      <c r="S17" s="180"/>
+      <c r="T17" s="181"/>
+    </row>
+    <row r="18" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B18" s="36"/>
       <c r="C18" s="37"/>
       <c r="D18" s="38"/>
@@ -9523,7 +9544,7 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
     </row>
-    <row r="19" spans="2:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="36"/>
       <c r="C19" s="37"/>
       <c r="D19" s="38"/>
@@ -9543,37 +9564,37 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="2:20" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="158" t="s">
+    <row r="20" spans="2:20" ht="28.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="157" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="160"/>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="160"/>
-      <c r="J20" s="160"/>
-      <c r="K20" s="160"/>
-      <c r="L20" s="160"/>
-      <c r="M20" s="160"/>
-      <c r="N20" s="160"/>
-      <c r="O20" s="160"/>
-      <c r="P20" s="160"/>
-      <c r="Q20" s="160"/>
-      <c r="R20" s="160"/>
-      <c r="S20" s="160"/>
-      <c r="T20" s="159"/>
-    </row>
-    <row r="21" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="C20" s="159"/>
+      <c r="D20" s="159"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="159"/>
+      <c r="H20" s="159"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="159"/>
+      <c r="L20" s="159"/>
+      <c r="M20" s="159"/>
+      <c r="N20" s="159"/>
+      <c r="O20" s="159"/>
+      <c r="P20" s="159"/>
+      <c r="Q20" s="159"/>
+      <c r="R20" s="159"/>
+      <c r="S20" s="159"/>
+      <c r="T20" s="158"/>
+    </row>
+    <row r="21" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="B21" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="165" t="s">
+      <c r="C21" s="195" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="165"/>
+      <c r="D21" s="195"/>
       <c r="E21" s="54" t="s">
         <v>201</v>
       </c>
@@ -9604,23 +9625,23 @@
       <c r="N21" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="O21" s="165" t="s">
+      <c r="O21" s="195" t="s">
         <v>91</v>
       </c>
-      <c r="P21" s="165"/>
-      <c r="Q21" s="165"/>
-      <c r="R21" s="165"/>
-      <c r="S21" s="165"/>
-      <c r="T21" s="166"/>
-    </row>
-    <row r="22" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P21" s="195"/>
+      <c r="Q21" s="195"/>
+      <c r="R21" s="195"/>
+      <c r="S21" s="195"/>
+      <c r="T21" s="196"/>
+    </row>
+    <row r="22" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B22" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="162">
+      <c r="C22" s="166">
         <v>46023</v>
       </c>
-      <c r="D22" s="163"/>
+      <c r="D22" s="167"/>
       <c r="E22" s="43">
         <v>47118</v>
       </c>
@@ -9651,23 +9672,23 @@
       <c r="N22" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O22" s="88" t="s">
+      <c r="O22" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="88"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="164"/>
-    </row>
-    <row r="23" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P22" s="170"/>
+      <c r="Q22" s="170"/>
+      <c r="R22" s="170"/>
+      <c r="S22" s="170"/>
+      <c r="T22" s="171"/>
+    </row>
+    <row r="23" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B23" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="162">
+      <c r="C23" s="166">
         <v>46023</v>
       </c>
-      <c r="D23" s="163"/>
+      <c r="D23" s="167"/>
       <c r="E23" s="43">
         <v>47118</v>
       </c>
@@ -9698,23 +9719,23 @@
       <c r="N23" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O23" s="88" t="s">
+      <c r="O23" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P23" s="88"/>
-      <c r="Q23" s="88"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="88"/>
-      <c r="T23" s="164"/>
-    </row>
-    <row r="24" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P23" s="170"/>
+      <c r="Q23" s="170"/>
+      <c r="R23" s="170"/>
+      <c r="S23" s="170"/>
+      <c r="T23" s="171"/>
+    </row>
+    <row r="24" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B24" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="162">
+      <c r="C24" s="166">
         <v>46023</v>
       </c>
-      <c r="D24" s="163"/>
+      <c r="D24" s="167"/>
       <c r="E24" s="43">
         <v>47118</v>
       </c>
@@ -9745,23 +9766,23 @@
       <c r="N24" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O24" s="88" t="s">
+      <c r="O24" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P24" s="88"/>
-      <c r="Q24" s="88"/>
-      <c r="R24" s="88"/>
-      <c r="S24" s="88"/>
-      <c r="T24" s="164"/>
-    </row>
-    <row r="25" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P24" s="170"/>
+      <c r="Q24" s="170"/>
+      <c r="R24" s="170"/>
+      <c r="S24" s="170"/>
+      <c r="T24" s="171"/>
+    </row>
+    <row r="25" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B25" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="162">
+      <c r="C25" s="166">
         <v>46023</v>
       </c>
-      <c r="D25" s="163"/>
+      <c r="D25" s="167"/>
       <c r="E25" s="43">
         <v>47118</v>
       </c>
@@ -9792,23 +9813,23 @@
       <c r="N25" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O25" s="88" t="s">
+      <c r="O25" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P25" s="88"/>
-      <c r="Q25" s="88"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="164"/>
-    </row>
-    <row r="26" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P25" s="170"/>
+      <c r="Q25" s="170"/>
+      <c r="R25" s="170"/>
+      <c r="S25" s="170"/>
+      <c r="T25" s="171"/>
+    </row>
+    <row r="26" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B26" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="162">
+      <c r="C26" s="166">
         <v>46023</v>
       </c>
-      <c r="D26" s="163"/>
+      <c r="D26" s="167"/>
       <c r="E26" s="43">
         <v>47118</v>
       </c>
@@ -9839,23 +9860,23 @@
       <c r="N26" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O26" s="88" t="s">
+      <c r="O26" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P26" s="88"/>
-      <c r="Q26" s="88"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="88"/>
-      <c r="T26" s="164"/>
-    </row>
-    <row r="27" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P26" s="170"/>
+      <c r="Q26" s="170"/>
+      <c r="R26" s="170"/>
+      <c r="S26" s="170"/>
+      <c r="T26" s="171"/>
+    </row>
+    <row r="27" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B27" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="162">
+      <c r="C27" s="166">
         <v>46023</v>
       </c>
-      <c r="D27" s="163"/>
+      <c r="D27" s="167"/>
       <c r="E27" s="43">
         <v>47118</v>
       </c>
@@ -9886,23 +9907,23 @@
       <c r="N27" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O27" s="88" t="s">
+      <c r="O27" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P27" s="88"/>
-      <c r="Q27" s="88"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="164"/>
-    </row>
-    <row r="28" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P27" s="170"/>
+      <c r="Q27" s="170"/>
+      <c r="R27" s="170"/>
+      <c r="S27" s="170"/>
+      <c r="T27" s="171"/>
+    </row>
+    <row r="28" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B28" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="162">
+      <c r="C28" s="166">
         <v>46023</v>
       </c>
-      <c r="D28" s="163"/>
+      <c r="D28" s="167"/>
       <c r="E28" s="43">
         <v>47118</v>
       </c>
@@ -9933,23 +9954,23 @@
       <c r="N28" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O28" s="88" t="s">
+      <c r="O28" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P28" s="88"/>
-      <c r="Q28" s="88"/>
-      <c r="R28" s="88"/>
-      <c r="S28" s="88"/>
-      <c r="T28" s="164"/>
-    </row>
-    <row r="29" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P28" s="170"/>
+      <c r="Q28" s="170"/>
+      <c r="R28" s="170"/>
+      <c r="S28" s="170"/>
+      <c r="T28" s="171"/>
+    </row>
+    <row r="29" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B29" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="162">
+      <c r="C29" s="166">
         <v>46023</v>
       </c>
-      <c r="D29" s="163"/>
+      <c r="D29" s="167"/>
       <c r="E29" s="43">
         <v>47118</v>
       </c>
@@ -9980,23 +10001,23 @@
       <c r="N29" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O29" s="88" t="s">
+      <c r="O29" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P29" s="88"/>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="88"/>
-      <c r="T29" s="164"/>
-    </row>
-    <row r="30" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P29" s="170"/>
+      <c r="Q29" s="170"/>
+      <c r="R29" s="170"/>
+      <c r="S29" s="170"/>
+      <c r="T29" s="171"/>
+    </row>
+    <row r="30" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B30" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="162">
+      <c r="C30" s="166">
         <v>46023</v>
       </c>
-      <c r="D30" s="163"/>
+      <c r="D30" s="167"/>
       <c r="E30" s="43">
         <v>47118</v>
       </c>
@@ -10027,23 +10048,23 @@
       <c r="N30" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O30" s="88" t="s">
+      <c r="O30" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P30" s="88"/>
-      <c r="Q30" s="88"/>
-      <c r="R30" s="88"/>
-      <c r="S30" s="88"/>
-      <c r="T30" s="164"/>
-    </row>
-    <row r="31" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P30" s="170"/>
+      <c r="Q30" s="170"/>
+      <c r="R30" s="170"/>
+      <c r="S30" s="170"/>
+      <c r="T30" s="171"/>
+    </row>
+    <row r="31" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B31" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="162">
+      <c r="C31" s="166">
         <v>46023</v>
       </c>
-      <c r="D31" s="163"/>
+      <c r="D31" s="167"/>
       <c r="E31" s="43">
         <v>47118</v>
       </c>
@@ -10074,23 +10095,23 @@
       <c r="N31" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O31" s="88" t="s">
+      <c r="O31" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P31" s="88"/>
-      <c r="Q31" s="88"/>
-      <c r="R31" s="88"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="164"/>
-    </row>
-    <row r="32" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P31" s="170"/>
+      <c r="Q31" s="170"/>
+      <c r="R31" s="170"/>
+      <c r="S31" s="170"/>
+      <c r="T31" s="171"/>
+    </row>
+    <row r="32" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B32" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="162">
+      <c r="C32" s="166">
         <v>46023</v>
       </c>
-      <c r="D32" s="163"/>
+      <c r="D32" s="167"/>
       <c r="E32" s="43">
         <v>47118</v>
       </c>
@@ -10121,23 +10142,23 @@
       <c r="N32" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O32" s="88" t="s">
+      <c r="O32" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P32" s="88"/>
-      <c r="Q32" s="88"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="88"/>
-      <c r="T32" s="164"/>
-    </row>
-    <row r="33" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P32" s="170"/>
+      <c r="Q32" s="170"/>
+      <c r="R32" s="170"/>
+      <c r="S32" s="170"/>
+      <c r="T32" s="171"/>
+    </row>
+    <row r="33" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B33" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="162">
+      <c r="C33" s="166">
         <v>46023</v>
       </c>
-      <c r="D33" s="163"/>
+      <c r="D33" s="167"/>
       <c r="E33" s="43">
         <v>47118</v>
       </c>
@@ -10168,23 +10189,23 @@
       <c r="N33" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O33" s="88" t="s">
+      <c r="O33" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P33" s="88"/>
-      <c r="Q33" s="88"/>
-      <c r="R33" s="88"/>
-      <c r="S33" s="88"/>
-      <c r="T33" s="164"/>
-    </row>
-    <row r="34" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P33" s="170"/>
+      <c r="Q33" s="170"/>
+      <c r="R33" s="170"/>
+      <c r="S33" s="170"/>
+      <c r="T33" s="171"/>
+    </row>
+    <row r="34" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B34" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="162">
+      <c r="C34" s="166">
         <v>46023</v>
       </c>
-      <c r="D34" s="163"/>
+      <c r="D34" s="167"/>
       <c r="E34" s="43">
         <v>47118</v>
       </c>
@@ -10215,23 +10236,23 @@
       <c r="N34" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="O34" s="88" t="s">
+      <c r="O34" s="170" t="s">
         <v>202</v>
       </c>
-      <c r="P34" s="88"/>
-      <c r="Q34" s="88"/>
-      <c r="R34" s="88"/>
-      <c r="S34" s="88"/>
-      <c r="T34" s="164"/>
-    </row>
-    <row r="35" spans="2:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P34" s="170"/>
+      <c r="Q34" s="170"/>
+      <c r="R34" s="170"/>
+      <c r="S34" s="170"/>
+      <c r="T34" s="171"/>
+    </row>
+    <row r="35" spans="2:20" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="172">
+      <c r="C35" s="178">
         <v>46023</v>
       </c>
-      <c r="D35" s="173"/>
+      <c r="D35" s="179"/>
       <c r="E35" s="48">
         <v>47118</v>
       </c>
@@ -10262,16 +10283,16 @@
       <c r="N35" s="50" t="s">
         <v>197</v>
       </c>
-      <c r="O35" s="174" t="s">
+      <c r="O35" s="180" t="s">
         <v>202</v>
       </c>
-      <c r="P35" s="174"/>
-      <c r="Q35" s="174"/>
-      <c r="R35" s="174"/>
-      <c r="S35" s="174"/>
-      <c r="T35" s="175"/>
-    </row>
-    <row r="36" spans="2:20" ht="18" x14ac:dyDescent="0.3">
+      <c r="P35" s="180"/>
+      <c r="Q35" s="180"/>
+      <c r="R35" s="180"/>
+      <c r="S35" s="180"/>
+      <c r="T35" s="181"/>
+    </row>
+    <row r="36" spans="2:20" ht="19" x14ac:dyDescent="0.2">
       <c r="B36" s="36"/>
       <c r="C36" s="37"/>
       <c r="D36" s="38"/>
@@ -10291,61 +10312,61 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
     </row>
-    <row r="37" spans="2:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L37" s="40"/>
     </row>
-    <row r="38" spans="2:20" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="185" t="s">
+    <row r="38" spans="2:20" ht="31.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="175" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="186"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="186"/>
-      <c r="H38" s="186"/>
-      <c r="I38" s="186"/>
-      <c r="J38" s="186"/>
-      <c r="K38" s="186"/>
-      <c r="L38" s="187"/>
-    </row>
-    <row r="39" spans="2:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="190" t="s">
+      <c r="C38" s="176"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
+      <c r="G38" s="176"/>
+      <c r="H38" s="176"/>
+      <c r="I38" s="176"/>
+      <c r="J38" s="176"/>
+      <c r="K38" s="176"/>
+      <c r="L38" s="177"/>
+    </row>
+    <row r="39" spans="2:20" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="184" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="192" t="s">
+      <c r="C39" s="186" t="s">
         <v>141</v>
       </c>
-      <c r="D39" s="193"/>
-      <c r="E39" s="192" t="s">
+      <c r="D39" s="187"/>
+      <c r="E39" s="186" t="s">
         <v>142</v>
       </c>
-      <c r="F39" s="193"/>
-      <c r="G39" s="196" t="s">
+      <c r="F39" s="187"/>
+      <c r="G39" s="190" t="s">
         <v>143</v>
       </c>
-      <c r="H39" s="188" t="s">
+      <c r="H39" s="182" t="s">
         <v>140</v>
       </c>
-      <c r="I39" s="189"/>
-      <c r="J39" s="182" t="s">
+      <c r="I39" s="183"/>
+      <c r="J39" s="172" t="s">
         <v>210</v>
       </c>
-      <c r="K39" s="183"/>
-      <c r="L39" s="184"/>
+      <c r="K39" s="173"/>
+      <c r="L39" s="174"/>
       <c r="N39" s="79" t="s">
         <v>233</v>
       </c>
       <c r="O39" s="79"/>
       <c r="P39" s="79"/>
     </row>
-    <row r="40" spans="2:20" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="191"/>
-      <c r="C40" s="194"/>
-      <c r="D40" s="195"/>
-      <c r="E40" s="194"/>
-      <c r="F40" s="195"/>
-      <c r="G40" s="197"/>
+    <row r="40" spans="2:20" ht="19.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="185"/>
+      <c r="C40" s="188"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="188"/>
+      <c r="F40" s="189"/>
+      <c r="G40" s="191"/>
       <c r="H40" s="63" t="s">
         <v>144</v>
       </c>
@@ -10362,18 +10383,18 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="161" t="s">
+      <c r="C41" s="168" t="s">
         <v>163</v>
       </c>
-      <c r="D41" s="161"/>
-      <c r="E41" s="161" t="s">
+      <c r="D41" s="168"/>
+      <c r="E41" s="168" t="s">
         <v>168</v>
       </c>
-      <c r="F41" s="161"/>
+      <c r="F41" s="168"/>
       <c r="G41" s="32">
         <v>46042</v>
       </c>
@@ -10393,18 +10414,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="161" t="s">
+      <c r="C42" s="168" t="s">
         <v>164</v>
       </c>
-      <c r="D42" s="161"/>
-      <c r="E42" s="176" t="s">
+      <c r="D42" s="168"/>
+      <c r="E42" s="169" t="s">
         <v>169</v>
       </c>
-      <c r="F42" s="176"/>
+      <c r="F42" s="169"/>
       <c r="G42" s="32">
         <v>46042</v>
       </c>
@@ -10424,18 +10445,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="161" t="s">
+      <c r="C43" s="168" t="s">
         <v>165</v>
       </c>
-      <c r="D43" s="161"/>
-      <c r="E43" s="176" t="s">
+      <c r="D43" s="168"/>
+      <c r="E43" s="169" t="s">
         <v>170</v>
       </c>
-      <c r="F43" s="176"/>
+      <c r="F43" s="169"/>
       <c r="G43" s="32">
         <v>46042</v>
       </c>
@@ -10455,18 +10476,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="161" t="s">
+      <c r="C44" s="168" t="s">
         <v>181</v>
       </c>
-      <c r="D44" s="161"/>
-      <c r="E44" s="176" t="s">
+      <c r="D44" s="168"/>
+      <c r="E44" s="169" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="176"/>
+      <c r="F44" s="169"/>
       <c r="G44" s="32">
         <v>46042</v>
       </c>
@@ -10486,18 +10507,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="161" t="s">
+      <c r="C45" s="168" t="s">
         <v>182</v>
       </c>
-      <c r="D45" s="161"/>
-      <c r="E45" s="176" t="s">
+      <c r="D45" s="168"/>
+      <c r="E45" s="169" t="s">
         <v>172</v>
       </c>
-      <c r="F45" s="176"/>
+      <c r="F45" s="169"/>
       <c r="G45" s="32">
         <v>46042</v>
       </c>
@@ -10517,18 +10538,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="161" t="s">
+      <c r="C46" s="168" t="s">
         <v>183</v>
       </c>
-      <c r="D46" s="161"/>
-      <c r="E46" s="176" t="s">
+      <c r="D46" s="168"/>
+      <c r="E46" s="169" t="s">
         <v>173</v>
       </c>
-      <c r="F46" s="176"/>
+      <c r="F46" s="169"/>
       <c r="G46" s="32">
         <v>46042</v>
       </c>
@@ -10548,18 +10569,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="161" t="s">
+      <c r="C47" s="168" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="161"/>
-      <c r="E47" s="176" t="s">
+      <c r="D47" s="168"/>
+      <c r="E47" s="169" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="176"/>
+      <c r="F47" s="169"/>
       <c r="G47" s="32">
         <v>46042</v>
       </c>
@@ -10579,18 +10600,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:20" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:20" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="161" t="s">
+      <c r="C48" s="168" t="s">
         <v>185</v>
       </c>
-      <c r="D48" s="161"/>
-      <c r="E48" s="176" t="s">
+      <c r="D48" s="168"/>
+      <c r="E48" s="169" t="s">
         <v>175</v>
       </c>
-      <c r="F48" s="176"/>
+      <c r="F48" s="169"/>
       <c r="G48" s="32">
         <v>46042</v>
       </c>
@@ -10610,18 +10631,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C49" s="161" t="s">
+      <c r="C49" s="168" t="s">
         <v>186</v>
       </c>
-      <c r="D49" s="161"/>
-      <c r="E49" s="176" t="s">
+      <c r="D49" s="168"/>
+      <c r="E49" s="169" t="s">
         <v>176</v>
       </c>
-      <c r="F49" s="176"/>
+      <c r="F49" s="169"/>
       <c r="G49" s="32">
         <v>46042</v>
       </c>
@@ -10641,18 +10662,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="C50" s="161" t="s">
+      <c r="C50" s="168" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="161"/>
-      <c r="E50" s="176" t="s">
+      <c r="D50" s="168"/>
+      <c r="E50" s="169" t="s">
         <v>177</v>
       </c>
-      <c r="F50" s="176"/>
+      <c r="F50" s="169"/>
       <c r="G50" s="32">
         <v>46042</v>
       </c>
@@ -10672,18 +10693,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="C51" s="161" t="s">
+      <c r="C51" s="168" t="s">
         <v>188</v>
       </c>
-      <c r="D51" s="161"/>
-      <c r="E51" s="176" t="s">
+      <c r="D51" s="168"/>
+      <c r="E51" s="169" t="s">
         <v>178</v>
       </c>
-      <c r="F51" s="176"/>
+      <c r="F51" s="169"/>
       <c r="G51" s="32">
         <v>46042</v>
       </c>
@@ -10706,18 +10727,18 @@
         <v>213</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="161" t="s">
+      <c r="C52" s="168" t="s">
         <v>189</v>
       </c>
-      <c r="D52" s="161"/>
-      <c r="E52" s="176" t="s">
+      <c r="D52" s="168"/>
+      <c r="E52" s="169" t="s">
         <v>179</v>
       </c>
-      <c r="F52" s="176"/>
+      <c r="F52" s="169"/>
       <c r="G52" s="32">
         <v>46042</v>
       </c>
@@ -10737,18 +10758,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="161" t="s">
+      <c r="C53" s="168" t="s">
         <v>190</v>
       </c>
-      <c r="D53" s="161"/>
-      <c r="E53" s="177" t="s">
+      <c r="D53" s="168"/>
+      <c r="E53" s="202" t="s">
         <v>180</v>
       </c>
-      <c r="F53" s="178"/>
+      <c r="F53" s="203"/>
       <c r="G53" s="32">
         <v>46042</v>
       </c>
@@ -10768,19 +10789,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="198" t="s">
+    <row r="54" spans="2:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="160" t="s">
         <v>136</v>
       </c>
-      <c r="C54" s="200" t="s">
+      <c r="C54" s="162" t="s">
         <v>137</v>
       </c>
-      <c r="D54" s="200"/>
-      <c r="E54" s="200" t="s">
+      <c r="D54" s="162"/>
+      <c r="E54" s="162" t="s">
         <v>138</v>
       </c>
-      <c r="F54" s="200"/>
-      <c r="G54" s="202">
+      <c r="F54" s="162"/>
+      <c r="G54" s="164">
         <v>45910</v>
       </c>
       <c r="H54" s="80">
@@ -10799,13 +10820,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="199"/>
-      <c r="C55" s="201"/>
-      <c r="D55" s="201"/>
-      <c r="E55" s="201"/>
-      <c r="F55" s="201"/>
-      <c r="G55" s="203"/>
+    <row r="55" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="161"/>
+      <c r="C55" s="163"/>
+      <c r="D55" s="163"/>
+      <c r="E55" s="163"/>
+      <c r="F55" s="163"/>
+      <c r="G55" s="165"/>
       <c r="H55" s="82" t="s">
         <v>236</v>
       </c>
@@ -10820,6 +10841,90 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="O28:T28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="O25:T25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="O26:T26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="O27:T27"/>
+    <mergeCell ref="O29:T29"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="O7:T7"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="O11:T11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="O8:T8"/>
+    <mergeCell ref="O12:T12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="O9:T9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="O10:T10"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="O23:T23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="O24:T24"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="B1:T1"/>
+    <mergeCell ref="B20:T20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="O15:T15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="O30:T30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="O31:T31"/>
+    <mergeCell ref="O32:T32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="O33:T33"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="O34:T34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="O35:T35"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:G40"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="C54:D55"/>
     <mergeCell ref="E54:F55"/>
@@ -10836,92 +10941,11 @@
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="O33:T33"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="O34:T34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="O35:T35"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="O30:T30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="O31:T31"/>
-    <mergeCell ref="O32:T32"/>
-    <mergeCell ref="B1:T1"/>
-    <mergeCell ref="B20:T20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="B2:T2"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="O23:T23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="O24:T24"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="O7:T7"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="O11:T11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="O8:T8"/>
-    <mergeCell ref="O12:T12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="O9:T9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="O10:T10"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="O28:T28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="O25:T25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="O26:T26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="O27:T27"/>
-    <mergeCell ref="O29:T29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C44:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>